--- a/outputs/SUEA_Safety_API_Inventory.xlsx
+++ b/outputs/SUEA_Safety_API_Inventory.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Summary" sheetId="1" r:id="Rfaf6b51798494eab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_API_Inventory" sheetId="2" r:id="Reb78a12de8ba4377"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Checkin_Locations" sheetId="3" r:id="R16ea2412ddf04053"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Safety_Effort" sheetId="4" r:id="R2a14c81d1dfa4441"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Safety_Culture" sheetId="5" r:id="R35c0924fe6be4d49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Uploads_Media" sheetId="6" r:id="R6eb78a445d5b4678"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Table_Mapping" sheetId="7" r:id="Ra2c9eba4bb9a49b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Payload_Response" sheetId="8" r:id="Rc9cc745e894b4bc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Scale_Rules" sheetId="9" r:id="R3b62dc6220d34469"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Backlog" sheetId="10" r:id="R8dfb09a0e44e4eca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_API_Counts" sheetId="11" r:id="R638fa1911d9447e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Summary" sheetId="1" r:id="R3e12936876c64d57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_API_Inventory" sheetId="2" r:id="R456d1015e98e45d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Checkin_Locations" sheetId="3" r:id="R4d90e715f2a34d3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Safety_Effort" sheetId="4" r:id="Rdc54cc0632924210"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Safety_Culture" sheetId="5" r:id="Rd6149dfc07bf48c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Uploads_Media" sheetId="6" r:id="Rade1f15d6f8944d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Table_Mapping" sheetId="7" r:id="R699245a09da94b6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Payload_Response" sheetId="8" r:id="R7442b8c89ae342b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Scale_Rules" sheetId="9" r:id="Re77241efbba3496e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Backlog" sheetId="10" r:id="R3ac98fa9b46744df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_API_Counts" sheetId="11" r:id="Rb330729848ef44fb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -107,7 +107,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -143,6 +143,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -409,16 +412,16 @@
         <x:v>Locations</x:v>
       </x:c>
       <x:c r="B4" s="4" t="str">
-        <x:v>มี /api/safety-effort/locations แบบรวม + type/search/limit</x:v>
+        <x:v>มี locations repository/API และ RMR SSO Plant sync design</x:v>
       </x:c>
       <x:c r="C4" s="4" t="str">
-        <x:v>แยก plants/offices/sites/map/search/detail</x:v>
+        <x:v>rmr_sso.Plant read-only → mirror CPAC; Admin Plant เก็บ source=ADMIN</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="E4" s="4" t="str">
-        <x:v>ข้อมูลหลักแสนห้ามโหลดรวม</x:v>
+        <x:v>ห้าม query ข้ามฐานทุก request และห้ามเขียน Plant Master</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -578,16 +581,16 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="B3" s="4" t="str">
-        <x:v>แยก locations API ตาม plants/offices/sites/map/search</x:v>
+        <x:v>ทำ RMR SSO Plant incremental sync เข้า CPAC mirror</x:v>
       </x:c>
       <x:c r="C3" s="4" t="str">
-        <x:v>ข้อมูลอาจหลักแสน โหลดรวมไม่ได้</x:v>
+        <x:v>Plant Master ต้อง read-only แต่ Check-in ต้องใช้ locations.id</x:v>
       </x:c>
       <x:c r="D3" s="4" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Backend/Infra</x:v>
       </x:c>
       <x:c r="E3" s="4" t="str">
-        <x:v>ทุกเส้นมี pagination/bbox/hard limit</x:v>
+        <x:v>sync upsert ได้, missing→INACTIVE, ไม่มี write ไป rmr_sso.Plant</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -598,13 +601,13 @@
         <x:v>ปรับ frontend check-in ให้เรียก API แทน mock/localStorage</x:v>
       </x:c>
       <x:c r="C4" s="4" t="str">
-        <x:v>ข้อมูลจริงต้องมาจาก DB</x:v>
+        <x:v>ข้อมูลจริงต้องมาจาก CPAC mirror และ Admin Plant API</x:v>
       </x:c>
       <x:c r="D4" s="4" t="str">
         <x:v>Frontend</x:v>
       </x:c>
       <x:c r="E4" s="4" t="str">
-        <x:v>เลือกโรงงาน/สำนักงาน/site จาก API ได้</x:v>
+        <x:v>เห็น source/readOnly, เลือก Check-in ด้วย local id และแก้ RMR Plant ไม่ได้</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -724,6 +727,57 @@
       </x:c>
       <x:c r="E11" s="4" t="str">
         <x:v>มี logs/metrics/rate limit ต่อ endpoint สำคัญ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="28" customHeight="1">
+      <x:c r="A12" s="14" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="str">
+        <x:v>เชื่อมหน้า Admin Plant กับ API</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="str">
+        <x:v>ปัจจุบันยังใช้ localStorage</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="str">
+        <x:v>เพิ่มโรงงานแล้ว source=ADMIN ใน CPAC และ refresh แล้วยังอยู่</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="28" customHeight="1">
+      <x:c r="A13" s="14" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="B13" s="14" t="str">
+        <x:v>บังคับ source read-only ใน PATCH/DELETE</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="str">
+        <x:v>ป้องกันแก้ RMR Master ผ่าน Safety</x:v>
+      </x:c>
+      <x:c r="D13" s="14" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="str">
+        <x:v>RMR_SSO_PLANT ตอบ 403 source_read_only</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="28" customHeight="1">
+      <x:c r="A14" s="14" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="B14" s="14" t="str">
+        <x:v>ตั้ง scheduled incremental Plant sync</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="str">
+        <x:v>ลดข้อมูลล้าสมัยและไม่ query ข้ามฐานทุก request</x:v>
+      </x:c>
+      <x:c r="D14" s="14" t="str">
+        <x:v>Infra/Backend</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="str">
+        <x:v>มี monitoring, retry และ import history</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -767,10 +821,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C2" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D2" s="4" t="n">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E2" s="4" t="str">
         <x:v>target design สำหรับ implement</x:v>
@@ -784,13 +838,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C3" s="4" t="n">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D3" s="4" t="n">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3" s="4" t="str">
-        <x:v>มีบางเส้นแล้วใน repo และมี target เพิ่ม</x:v>
+        <x:v>Plant ใช้ CPAC mirror; RMR read-only และ Admin editable</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -835,10 +889,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D6" s="4" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="4" t="str">
         <x:v>target design สำหรับ implement</x:v>
@@ -971,10 +1025,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C14" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D14" s="4" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
         <x:v>target design สำหรับ implement</x:v>
@@ -1107,10 +1161,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C22" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D22" s="4" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
         <x:v>target design สำหรับ implement</x:v>
@@ -1124,10 +1178,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C23" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D23" s="4" t="n">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="D23" s="4" t="n">
-        <x:v>2</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
         <x:v>target design สำหรับ implement</x:v>
@@ -1192,10 +1246,10 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="C27" s="4" t="n">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D27" s="4" t="n">
-        <x:v>144</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
         <x:v>จำนวนเส้นใน inventory sheet</x:v>
@@ -1290,7 +1344,7 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K2" s="4" t="str">
-        <x:v>มีแล้วใน repo</x:v>
+        <x:v>มี implementation ใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1325,7 +1379,7 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K3" s="4" t="str">
-        <x:v>มีแล้วใน repo</x:v>
+        <x:v>มี implementation ใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1360,7 +1414,7 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K4" s="4" t="str">
-        <x:v>มีแล้วใน repo</x:v>
+        <x:v>มี implementation ใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1368,7 +1422,7 @@
         <x:v>Auth</x:v>
       </x:c>
       <x:c r="B5" s="4" t="str">
-        <x:v>POST</x:v>
+        <x:v>GET</x:v>
       </x:c>
       <x:c r="C5" s="4" t="str">
         <x:v>/api/auth/logout</x:v>
@@ -1380,7 +1434,7 @@
         <x:v>Header/Profile</x:v>
       </x:c>
       <x:c r="F5" s="4" t="str">
-        <x:v>เมื่อกด logout</x:v>
+        <x:v>เมื่อผู้ใช้เปิด logout endpoint</x:v>
       </x:c>
       <x:c r="G5" s="4" t="str">
         <x:v>User</x:v>
@@ -1395,7 +1449,7 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K5" s="4" t="str">
-        <x:v>มีแล้วใน repo</x:v>
+        <x:v>มี dedicated route และล้าง session cookie</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1430,7 +1484,7 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K6" s="4" t="str">
-        <x:v>มีแล้วใน repo</x:v>
+        <x:v>มี implementation ใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1444,7 +1498,7 @@
         <x:v>/api/locations/plants</x:v>
       </x:c>
       <x:c r="D7" s="4" t="str">
-        <x:v>รายการโรงงานสำหรับ check-in/search</x:v>
+        <x:v>รายการโรงงานจาก CPAC mirror รวม RMR SSO Plant และ Admin Plant</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
         <x:v>Check-in, Admin</x:v>
@@ -1462,10 +1516,10 @@
         <x:v>High if unpaged</x:v>
       </x:c>
       <x:c r="J7" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K7" s="4" t="str">
-        <x:v>แยกจาก all locations เพราะข้อมูลเยอะ</x:v>
+        <x:v>อ่าน CPAC locations; คืน source, externalKey, readOnly; ไม่ query rmr_sso ทุก request</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1497,7 +1551,7 @@
         <x:v>High if unpaged</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K8" s="4" t="str">
         <x:v>แยกประเภทเพื่อ index/cache ได้ดี</x:v>
@@ -1532,7 +1586,7 @@
         <x:v>High if unpaged</x:v>
       </x:c>
       <x:c r="J9" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K9" s="4" t="str">
         <x:v>site อาจเปลี่ยนบ่อยและมีปริมาณมาก</x:v>
@@ -1567,7 +1621,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J10" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K10" s="4" t="str">
         <x:v>รองรับ location นอก master</x:v>
@@ -1602,7 +1656,7 @@
         <x:v>Critical if returns all</x:v>
       </x:c>
       <x:c r="J11" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K11" s="4" t="str">
         <x:v>ต้องใช้ spatial index</x:v>
@@ -1637,7 +1691,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J12" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K12" s="4" t="str">
         <x:v>ค้นด้วย code/name/external key</x:v>
@@ -1672,7 +1726,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J13" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K13" s="4" t="str">
         <x:v>โหลด detail แยกจาก list</x:v>
@@ -1689,7 +1743,7 @@
         <x:v>/api/locations</x:v>
       </x:c>
       <x:c r="D14" s="4" t="str">
-        <x:v>เพิ่ม location ใหม่</x:v>
+        <x:v>เพิ่ม location; ถ้า type=PLANT บังคับ source=ADMIN</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
         <x:v>Admin</x:v>
@@ -1707,10 +1761,10 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J14" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K14" s="4" t="str">
-        <x:v>เขียนลง locations</x:v>
+        <x:v>เขียน CPAC_Safety.locations; Plant Admin ไม่เขียนกลับ rmr_sso.Plant</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1724,7 +1778,7 @@
         <x:v>/api/locations/:id</x:v>
       </x:c>
       <x:c r="D15" s="4" t="str">
-        <x:v>แก้ไข location</x:v>
+        <x:v>แก้ไข location ที่ source อนุญาต</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
         <x:v>Admin</x:v>
@@ -1742,10 +1796,10 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J15" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K15" s="4" t="str">
-        <x:v>ต้อง audit</x:v>
+        <x:v>อนุญาต ADMIN/USER ตามสิทธิ์; RMR_SSO_PLANT ต้องตอบ 403 source_read_only</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1759,7 +1813,7 @@
         <x:v>/api/locations/:id</x:v>
       </x:c>
       <x:c r="D16" s="4" t="str">
-        <x:v>soft delete location</x:v>
+        <x:v>soft delete location ที่ source อนุญาต</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
         <x:v>Admin</x:v>
@@ -1777,10 +1831,10 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J16" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K16" s="4" t="str">
-        <x:v>soft delete เท่านั้น</x:v>
+        <x:v>อนุญาต ADMIN/USER ตามสิทธิ์; RMR_SSO_PLANT ต้องตอบ 403 source_read_only</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1987,7 +2041,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J22" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K22" s="4" t="str">
         <x:v>คืน checkinId เพื่อเริ่มกิจกรรม</x:v>
@@ -2022,7 +2076,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J23" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K23" s="4" t="str">
         <x:v>filter ตามวันที่</x:v>
@@ -2057,7 +2111,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="J24" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K24" s="4" t="str">
         <x:v>ต้องมี indexes ตาม user/date/location</x:v>
@@ -2092,7 +2146,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J25" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K25" s="4" t="str">
         <x:v>รวม attachments summary</x:v>
@@ -2722,7 +2776,7 @@
         <x:v>High if unpaged</x:v>
       </x:c>
       <x:c r="J43" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K43" s="4" t="str">
         <x:v>แทน localStorage posts</x:v>
@@ -2757,7 +2811,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J44" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K44" s="4" t="str">
         <x:v>ส่ง attachmentIds ไม่ส่ง base64</x:v>
@@ -2792,7 +2846,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J45" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K45" s="4" t="str">
         <x:v>รวม comments page แรก</x:v>
@@ -2827,7 +2881,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J46" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K46" s="4" t="str">
         <x:v>optional</x:v>
@@ -2862,7 +2916,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J47" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K47" s="4" t="str">
         <x:v>soft delete</x:v>
@@ -2897,7 +2951,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J48" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K48" s="4" t="str">
         <x:v>ให้คะแนนตาม rule</x:v>
@@ -2932,7 +2986,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J49" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K49" s="4" t="str">
         <x:v>แยกจาก feed</x:v>
@@ -2967,7 +3021,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J50" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K50" s="4" t="str">
         <x:v>upsert reaction</x:v>
@@ -3002,7 +3056,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J51" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K51" s="4" t="str">
         <x:v>delete reaction</x:v>
@@ -3282,7 +3336,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J59" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K59" s="4" t="str">
         <x:v>บันทึก attempt</x:v>
@@ -3354,7 +3408,7 @@
       <x:c r="J61" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K61" s="4" t="str"/>
+      <x:c r="K61" s="4"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="4" t="str">
@@ -3667,7 +3721,7 @@
       <x:c r="J70" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K70" s="4" t="str"/>
+      <x:c r="K70" s="4"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="4" t="str">
@@ -3910,7 +3964,7 @@
       <x:c r="J77" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K77" s="4" t="str"/>
+      <x:c r="K77" s="4"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="4" t="str">
@@ -3978,7 +4032,7 @@
       <x:c r="J79" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K79" s="4" t="str"/>
+      <x:c r="K79" s="4"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="4" t="str">
@@ -4011,7 +4065,7 @@
       <x:c r="J80" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K80" s="4" t="str"/>
+      <x:c r="K80" s="4"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="4" t="str">
@@ -4044,7 +4098,7 @@
       <x:c r="J81" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K81" s="4" t="str"/>
+      <x:c r="K81" s="4"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="4" t="str">
@@ -4077,7 +4131,7 @@
       <x:c r="J82" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K82" s="4" t="str"/>
+      <x:c r="K82" s="4"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="4" t="str">
@@ -4160,13 +4214,13 @@
         <x:v>/api/location-imports</x:v>
       </x:c>
       <x:c r="D85" s="4" t="str">
-        <x:v>upload/import master location file</x:v>
+        <x:v>เริ่ม import/sync location master</x:v>
       </x:c>
       <x:c r="E85" s="4" t="str">
-        <x:v>Admin</x:v>
+        <x:v>Admin/Scheduled job</x:v>
       </x:c>
       <x:c r="F85" s="4" t="str">
-        <x:v>admin import DataOcean/Excel</x:v>
+        <x:v>Admin import หรือ incremental RMR Plant sync</x:v>
       </x:c>
       <x:c r="G85" s="4" t="str">
         <x:v>Admin</x:v>
@@ -4181,7 +4235,7 @@
         <x:v>Target</x:v>
       </x:c>
       <x:c r="K85" s="4" t="str">
-        <x:v>สร้าง batch</x:v>
+        <x:v>รองรับ body {source:"RMR_SSO_PLANT"}; SELECT-only แล้ว upsert CPAC mirror</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -4215,7 +4269,7 @@
       <x:c r="J86" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K86" s="4" t="str"/>
+      <x:c r="K86" s="4"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="4" t="str">
@@ -4318,7 +4372,7 @@
       <x:c r="J89" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K89" s="4" t="str"/>
+      <x:c r="K89" s="4"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="4" t="str">
@@ -4456,7 +4510,7 @@
       <x:c r="J93" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K93" s="4" t="str"/>
+      <x:c r="K93" s="4"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="4" t="str">
@@ -4524,7 +4578,7 @@
       <x:c r="J95" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K95" s="4" t="str"/>
+      <x:c r="K95" s="4"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="4" t="str">
@@ -4592,7 +4646,7 @@
       <x:c r="J97" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K97" s="4" t="str"/>
+      <x:c r="K97" s="4"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="4" t="str">
@@ -4660,7 +4714,7 @@
       <x:c r="J99" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K99" s="4" t="str"/>
+      <x:c r="K99" s="4"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="4" t="str">
@@ -4693,7 +4747,7 @@
       <x:c r="J100" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K100" s="4" t="str"/>
+      <x:c r="K100" s="4"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="4" t="str">
@@ -4726,7 +4780,7 @@
       <x:c r="J101" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K101" s="4" t="str"/>
+      <x:c r="K101" s="4"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="4" t="str">
@@ -4759,7 +4813,7 @@
       <x:c r="J102" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K102" s="4" t="str"/>
+      <x:c r="K102" s="4"/>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="4" t="str">
@@ -4897,7 +4951,7 @@
       <x:c r="J106" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K106" s="4" t="str"/>
+      <x:c r="K106" s="4"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="4" t="str">
@@ -4965,7 +5019,7 @@
       <x:c r="J108" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K108" s="4" t="str"/>
+      <x:c r="K108" s="4"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="4" t="str">
@@ -4998,7 +5052,7 @@
       <x:c r="J109" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K109" s="4" t="str"/>
+      <x:c r="K109" s="4"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="4" t="str">
@@ -5031,7 +5085,7 @@
       <x:c r="J110" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K110" s="4" t="str"/>
+      <x:c r="K110" s="4"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="4" t="str">
@@ -5099,7 +5153,7 @@
       <x:c r="J112" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K112" s="4" t="str"/>
+      <x:c r="K112" s="4"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="4" t="str">
@@ -5167,7 +5221,7 @@
       <x:c r="J114" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K114" s="4" t="str"/>
+      <x:c r="K114" s="4"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="4" t="str">
@@ -5235,7 +5289,7 @@
       <x:c r="J116" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K116" s="4" t="str"/>
+      <x:c r="K116" s="4"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="4" t="str">
@@ -5268,7 +5322,7 @@
       <x:c r="J117" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K117" s="4" t="str"/>
+      <x:c r="K117" s="4"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="4" t="str">
@@ -5336,7 +5390,7 @@
       <x:c r="J119" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K119" s="4" t="str"/>
+      <x:c r="K119" s="4"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="4" t="str">
@@ -5369,7 +5423,7 @@
       <x:c r="J120" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K120" s="4" t="str"/>
+      <x:c r="K120" s="4"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="4" t="str">
@@ -5472,7 +5526,7 @@
       <x:c r="J123" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K123" s="4" t="str"/>
+      <x:c r="K123" s="4"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="4" t="str">
@@ -5505,7 +5559,7 @@
       <x:c r="J124" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K124" s="4" t="str"/>
+      <x:c r="K124" s="4"/>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="4" t="str">
@@ -5536,9 +5590,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J125" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K125" s="4" t="str"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K125" s="4" t="str">
+        <x:v>มี implementation ใน repo</x:v>
+      </x:c>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="4" t="str">
@@ -5569,9 +5625,11 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J126" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K126" s="4" t="str"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K126" s="4" t="str">
+        <x:v>มี implementation ใน repo</x:v>
+      </x:c>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="4" t="str">
@@ -5602,9 +5660,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J127" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K127" s="4" t="str"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K127" s="4" t="str">
+        <x:v>มี implementation ใน repo</x:v>
+      </x:c>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="4" t="str">
@@ -5670,7 +5730,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J129" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K129" s="4" t="str">
         <x:v>audit + reason required</x:v>
@@ -5742,7 +5802,7 @@
       <x:c r="J131" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K131" s="4" t="str"/>
+      <x:c r="K131" s="4"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="4" t="str">
@@ -5810,7 +5870,7 @@
       <x:c r="J133" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K133" s="4" t="str"/>
+      <x:c r="K133" s="4"/>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="4" t="str">
@@ -5913,7 +5973,7 @@
       <x:c r="J136" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K136" s="4" t="str"/>
+      <x:c r="K136" s="4"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="4" t="str">
@@ -5946,7 +6006,7 @@
       <x:c r="J137" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K137" s="4" t="str"/>
+      <x:c r="K137" s="4"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="4" t="str">
@@ -5979,7 +6039,7 @@
       <x:c r="J138" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K138" s="4" t="str"/>
+      <x:c r="K138" s="4"/>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="4" t="str">
@@ -6047,7 +6107,7 @@
       <x:c r="J140" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K140" s="4" t="str"/>
+      <x:c r="K140" s="4"/>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="4" t="str">
@@ -6080,7 +6140,7 @@
       <x:c r="J141" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K141" s="4" t="str"/>
+      <x:c r="K141" s="4"/>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="4" t="str">
@@ -6148,7 +6208,7 @@
       <x:c r="J143" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K143" s="4" t="str"/>
+      <x:c r="K143" s="4"/>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="4" t="str">
@@ -6181,7 +6241,7 @@
       <x:c r="J144" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K144" s="4" t="str"/>
+      <x:c r="K144" s="4"/>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="4" t="str">
@@ -6214,7 +6274,7 @@
       <x:c r="J145" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K145" s="4" t="str"/>
+      <x:c r="K145" s="4"/>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="4" t="str">
@@ -6247,7 +6307,7 @@
       <x:c r="J146" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K146" s="4" t="str"/>
+      <x:c r="K146" s="4"/>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="4" t="str">
@@ -6280,7 +6340,7 @@
       <x:c r="J147" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K147" s="4" t="str"/>
+      <x:c r="K147" s="4"/>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="4" t="str">
@@ -6313,7 +6373,7 @@
       <x:c r="J148" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K148" s="4" t="str"/>
+      <x:c r="K148" s="4"/>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="4" t="str">
@@ -6381,7 +6441,7 @@
       <x:c r="J150" s="10" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="K150" s="4" t="str"/>
+      <x:c r="K150" s="4"/>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="4" t="str">
@@ -6552,9 +6612,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J155" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K155" s="4" t="str"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K155" s="4" t="str">
+        <x:v>มี implementation ใน repo</x:v>
+      </x:c>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="4" t="str">
@@ -6585,9 +6647,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J156" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K156" s="4" t="str"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K156" s="4" t="str">
+        <x:v>มี implementation ใน repo</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6665,13 +6729,13 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="H2" s="4" t="str">
-        <x:v>location_type + status + name/code</x:v>
+        <x:v>CPAC locations mirror; source + external_key unique</x:v>
       </x:c>
       <x:c r="I2" s="4" t="str">
-        <x:v>โหลดเฉพาะ tab โรงงาน</x:v>
+        <x:v>แสดง badge RMR/Admin และปิดแก้ไขเมื่อ readOnly=true</x:v>
       </x:c>
       <x:c r="J2" s="4" t="str">
-        <x:v>โรงงานเยอะและใช้ filter เฉพาะ</x:v>
+        <x:v>ไม่ query rmr_sso.Plant ทุก request; ใช้ local ID สำหรับ Check-in</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -7615,13 +7679,13 @@
         <x:v>locations</x:v>
       </x:c>
       <x:c r="C2" s="4" t="str">
-        <x:v>organizations</x:v>
+        <x:v>plant_location_details, organizations</x:v>
       </x:c>
       <x:c r="D2" s="4" t="str">
         <x:v>Read</x:v>
       </x:c>
       <x:c r="E2" s="4" t="str">
-        <x:v>filter location_type</x:v>
+        <x:v>Plant อ่าน CPAC mirror; source=RMR_SSO_PLANT read-only, source=ADMIN editable</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -7928,6 +7992,23 @@
       </x:c>
       <x:c r="E20" s="4" t="str">
         <x:v>SSO backed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="28" customHeight="1">
+      <x:c r="A21" s="14" t="str">
+        <x:v>POST /api/location-imports {source=RMR_SSO_PLANT}</x:v>
+      </x:c>
+      <x:c r="B21" s="14" t="str">
+        <x:v>location_import_batches, location_import_rows</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="str">
+        <x:v>rmr_sso.Plant (SELECT-only), locations, plant_location_details</x:v>
+      </x:c>
+      <x:c r="D21" s="14" t="str">
+        <x:v>Read external / Write CPAC</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="str">
+        <x:v>incremental upsert by source + external_key; missing source rows become INACTIVE</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7981,10 +8062,10 @@
         <x:v>?type=PLANT&amp;bbox=100.1,13.1,100.9,14.0&amp;zoom=10</x:v>
       </x:c>
       <x:c r="C3" s="4" t="str">
-        <x:v>{"ok":true,"data":{"locations":[{"id":"500","nameTh":"...","lat":13.8,"lng":100.5}]}}</x:v>
+        <x:v>{"ok":true,"data":{"locations":[{"id":"500","nameTh":"...","source":"RMR_SSO_PLANT","externalKey":"13A1","readOnly":true,"lat":13.8,"lng":100.5}]}}</x:v>
       </x:c>
       <x:c r="D3" s="4" t="str">
-        <x:v>bbox required; cap markers</x:v>
+        <x:v>bbox required; cap markers; Plant ใช้ CPAC mirror</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -8055,6 +8136,48 @@
       </x:c>
       <x:c r="D8" s="4" t="str">
         <x:v>admin only; no original photos in list</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="28" customHeight="1">
+      <x:c r="A9" s="14" t="str">
+        <x:v>GET /api/locations/plants</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="str">
+        <x:v>?page=1&amp;pageSize=50&amp;search=คลองเตย</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="str">
+        <x:v>{"ok":true,"data":{"items":[{"id":"500","source":"RMR_SSO_PLANT","externalKey":"13A1","readOnly":true}]}}</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="str">
+        <x:v>อ่านจาก CPAC mirror และใช้ local id สำหรับ Map/Check-in</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="28" customHeight="1">
+      <x:c r="A10" s="14" t="str">
+        <x:v>POST /api/locations</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="str">
+        <x:v>{"locationType":"PLANT","code":"ADM-001","nameTh":"โรงงานใหม่","lat":13.7,"lng":100.5}</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="str">
+        <x:v>{"ok":true,"data":{"location":{"source":"ADMIN","readOnly":false}}}</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="str">
+        <x:v>Server บังคับ source=ADMIN และเก็บ created_by</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="28" customHeight="1">
+      <x:c r="A11" s="14" t="str">
+        <x:v>POST /api/location-imports</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="str">
+        <x:v>{"source":"RMR_SSO_PLANT","mode":"incremental"}</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="str">
+        <x:v>{"ok":true,"data":{"importId":"1001","status":"PROCESSING"}}</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="str">
+        <x:v>อ่าน RMR แบบ SELECT-only; upsert CPAC; missing rows → INACTIVE</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8189,13 +8312,13 @@
         <x:v>Caching</x:v>
       </x:c>
       <x:c r="B9" s="4" t="str">
-        <x:v>cache master/read-heavy endpoints</x:v>
+        <x:v>Plant list อ่าน CPAC mirror และ cache read-heavy endpoints</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
-        <x:v>ลด load</x:v>
+        <x:v>หลีกเลี่ยง cross-database query ทุก request</x:v>
       </x:c>
       <x:c r="D9" s="4" t="str">
-        <x:v>templates, rewards, leaderboard, location metadata</x:v>
+        <x:v>RMR Plant sync, templates, rewards, leaderboard</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -8217,13 +8340,41 @@
         <x:v>Audit</x:v>
       </x:c>
       <x:c r="B11" s="4" t="str">
-        <x:v>write/admin endpoints ต้อง audit</x:v>
+        <x:v>write/admin endpoints และ Plant sync ต้อง audit</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
-        <x:v>traceability</x:v>
+        <x:v>traceability และแยกข้อมูล Master/ADMIN</x:v>
       </x:c>
       <x:c r="D11" s="4" t="str">
-        <x:v>admin CRUD, rewards, events, locations</x:v>
+        <x:v>location sync, admin CRUD, rewards, events</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="28" customHeight="1">
+      <x:c r="A12" s="14" t="str">
+        <x:v>External DB</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="str">
+        <x:v>RMR_SSO_DATABASE_URL ใช้ pool แยกและ SELECT เฉพาะ rmr_sso.Plant</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="str">
+        <x:v>จำกัด blast radius และป้องกันแก้ Master</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="str">
+        <x:v>Plant sync job</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="28" customHeight="1">
+      <x:c r="A13" s="14" t="str">
+        <x:v>Sync key</x:v>
+      </x:c>
+      <x:c r="B13" s="14" t="str">
+        <x:v>Upsert ด้วย source + external_key และเปลี่ยน missing rows เป็น INACTIVE</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="str">
+        <x:v>ป้องกันข้อมูลซ้ำและรักษาประวัติ</x:v>
+      </x:c>
+      <x:c r="D13" s="14" t="str">
+        <x:v>locations</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/outputs/SUEA_Safety_API_Inventory.xlsx
+++ b/outputs/SUEA_Safety_API_Inventory.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Summary" sheetId="1" r:id="R3e12936876c64d57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_API_Inventory" sheetId="2" r:id="R456d1015e98e45d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Checkin_Locations" sheetId="3" r:id="R4d90e715f2a34d3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Safety_Effort" sheetId="4" r:id="Rdc54cc0632924210"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Safety_Culture" sheetId="5" r:id="Rd6149dfc07bf48c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Uploads_Media" sheetId="6" r:id="Rade1f15d6f8944d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Table_Mapping" sheetId="7" r:id="R699245a09da94b6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Payload_Response" sheetId="8" r:id="R7442b8c89ae342b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Scale_Rules" sheetId="9" r:id="Re77241efbba3496e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Backlog" sheetId="10" r:id="R3ac98fa9b46744df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_API_Counts" sheetId="11" r:id="Rb330729848ef44fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Summary" sheetId="1" r:id="R805a135cf29242a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_API_Inventory" sheetId="2" r:id="Re3500e4d27b240db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Checkin_Locations" sheetId="3" r:id="R820674c7670341f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Safety_Effort" sheetId="4" r:id="R485fff4b8d044e99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Safety_Culture" sheetId="5" r:id="Rf93f845988004b8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Uploads_Media" sheetId="6" r:id="Rbb441ddfd27d44e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Table_Mapping" sheetId="7" r:id="Rc6390266ba434255"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Payload_Response" sheetId="8" r:id="Rb6ae854fe1a3498e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Scale_Rules" sheetId="9" r:id="R54bdd13627244530"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Backlog" sheetId="10" r:id="R72dd7d25b86e452b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_API_Counts" sheetId="11" r:id="Rbeecddf81325478c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -378,16 +378,16 @@
         <x:v>Backend structure</x:v>
       </x:c>
       <x:c r="B2" s="4" t="str">
-        <x:v>Next.js API routes + backend/components</x:v>
+        <x:v>API catalog 159 routes ต่อ backend/components และฐานจริง</x:v>
       </x:c>
       <x:c r="C2" s="4" t="str">
-        <x:v>จัด src/app/api เป็น HTTP layer และ logic ใน backend/components/*</x:v>
+        <x:v>คง HTTP layer บางและแยก repository/persistence ตาม feature</x:v>
       </x:c>
       <x:c r="D2" s="10" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="E2" s="4" t="str">
-        <x:v>logic กระจายถ้า API เยอะขึ้น</x:v>
+        <x:v>ต้องทดสอบสิทธิ์ด้วย session จริง</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -395,7 +395,7 @@
         <x:v>Auth</x:v>
       </x:c>
       <x:c r="B3" s="4" t="str">
-        <x:v>SSO routes มีแล้ว</x:v>
+        <x:v>SSO/session/users ต่อฐานจริงแล้ว และแก้ profile_image_url เกินความยาว</x:v>
       </x:c>
       <x:c r="C3" s="4" t="str">
         <x:v>ใช้ session guard เดียวกันทุก API</x:v>
@@ -404,7 +404,7 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="E3" s="4" t="str">
-        <x:v>สิทธิ์ admin/user ต้องชัด</x:v>
+        <x:v>ต้อง monitor callback และ schema drift</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -412,16 +412,16 @@
         <x:v>Locations</x:v>
       </x:c>
       <x:c r="B4" s="4" t="str">
-        <x:v>มี locations repository/API และ RMR SSO Plant sync design</x:v>
+        <x:v>Locations/Plant mirror/Admin CRUD ต่อฐานจริงแล้ว</x:v>
       </x:c>
       <x:c r="C4" s="4" t="str">
-        <x:v>rmr_sso.Plant read-only → mirror CPAC; Admin Plant เก็บ source=ADMIN</x:v>
+        <x:v>rmr_sso.Plant read-only → CPAC mirror; Admin Plant source=ADMIN</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="E4" s="4" t="str">
-        <x:v>ห้าม query ข้ามฐานทุก request และห้ามเขียน Plant Master</x:v>
+        <x:v>RMR source ห้ามแก้/ลบ</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -429,16 +429,16 @@
         <x:v>Check-in</x:v>
       </x:c>
       <x:c r="B5" s="4" t="str">
-        <x:v>UI มี mock/preset และ local state</x:v>
+        <x:v>หน้า Check-in โหลด locations และ POST checkins จริง</x:v>
       </x:c>
       <x:c r="C5" s="4" t="str">
-        <x:v>POST /api/checkins + history/admin list</x:v>
+        <x:v>ใช้ CPAC local location id และ GPS จริง</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="E5" s="4" t="str">
-        <x:v>ยังไม่ persist จริง</x:v>
+        <x:v>ต้องได้รับสิทธิ์ geolocation</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -446,16 +446,16 @@
         <x:v>Safety Effort</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>หลาย flow ยังอยู่ localStorage</x:v>
+        <x:v>Admin/Linewalk/Assessment ใช้ API และ feature tables จริง</x:v>
       </x:c>
       <x:c r="C6" s="4" t="str">
-        <x:v>activities, assessment-runs, reports, findings APIs</x:v>
+        <x:v>activities, runs, answers, findings/actions/comments</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="E6" s="4" t="str">
-        <x:v>รายงานจริง/รูปยังไม่พร้อม</x:v>
+        <x:v>ตรวจ workflow/permission รายบทบาท</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -463,16 +463,16 @@
         <x:v>Safety Culture</x:v>
       </x:c>
       <x:c r="B7" s="4" t="str">
-        <x:v>posts/events/rewards หลายส่วนอยู่ provider/localStorage</x:v>
+        <x:v>posts/events/rewards/teams/awareness ใช้ API และฐานจริง</x:v>
       </x:c>
       <x:c r="C7" s="4" t="str">
-        <x:v>posts/comments/reactions/events/rewards APIs</x:v>
+        <x:v>ไม่มี mock/localStorage ใน production flow</x:v>
       </x:c>
       <x:c r="D7" s="10" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
-        <x:v>ข้อมูลหายข้ามเครื่อง</x:v>
+        <x:v>redeem ต้องอยู่ใน DB transaction</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -480,16 +480,16 @@
         <x:v>Media/images</x:v>
       </x:c>
       <x:c r="B8" s="4" t="str">
-        <x:v>base64/dataUrl ใน state/localStorage</x:v>
+        <x:v>uploads เก็บไฟล์จริงและ metadata ใน media_assets</x:v>
       </x:c>
       <x:c r="C8" s="4" t="str">
-        <x:v>object storage + media metadata + attachment IDs</x:v>
+        <x:v>owner_type/owner_id/link_type ผูกกับข้อมูลธุรกิจ</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="E8" s="4" t="str">
-        <x:v>DB/browser/storage หนักถ้าใช้ base64</x:v>
+        <x:v>กำหนด storage retention และ access</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -497,16 +497,16 @@
         <x:v>Reports/export</x:v>
       </x:c>
       <x:c r="B9" s="4" t="str">
-        <x:v>localStorage + mock records</x:v>
+        <x:v>export_jobs เก็บสถานะและผลลัพธ์จริง</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
-        <x:v>paginated report + async export</x:v>
+        <x:v>ดาวน์โหลดจาก job/result ไม่สร้าง mock response</x:v>
       </x:c>
       <x:c r="D9" s="10" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
-        <x:v>ข้อมูลเยอะทำ timeout</x:v>
+        <x:v>งานใหญ่ควร background</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -514,7 +514,7 @@
         <x:v>Scale rules</x:v>
       </x:c>
       <x:c r="B10" s="4" t="str">
-        <x:v>limit บางเส้นมีแต่ยังไม่ครบ</x:v>
+        <x:v>list endpoints มี limit และ Plant อ่าน CPAC mirror</x:v>
       </x:c>
       <x:c r="C10" s="4" t="str">
         <x:v>pagination/bbox/index/cache ทุกเส้น list</x:v>
@@ -523,7 +523,7 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="E10" s="4" t="str">
-        <x:v>full scan/full payload</x:v>
+        <x:v>ติดตาม slow query</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -780,6 +780,57 @@
         <x:v>มี monitoring, retry และ import history</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" ht="28" customHeight="1">
+      <x:c r="A15" s="14" t="str">
+        <x:v>DONE</x:v>
+      </x:c>
+      <x:c r="B15" s="14" t="str">
+        <x:v>ย้าย feature JSON ออกจาก audit_logs</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="str">
+        <x:v>สร้าง 8 ตารางจริงและ migration แล้ว</x:v>
+      </x:c>
+      <x:c r="D15" s="14" t="str">
+        <x:v>Backend/DB</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="str">
+        <x:v>audit_logs เหลือ audit trail เท่านั้น</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="28" customHeight="1">
+      <x:c r="A16" s="14" t="str">
+        <x:v>DONE</x:v>
+      </x:c>
+      <x:c r="B16" s="14" t="str">
+        <x:v>เชื่อมเมนูที่เปิดใช้งานกับ API จริง</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="str">
+        <x:v>Check-in, Safety Effort/Admin, Safety Culture, Notifications, Profile</x:v>
+      </x:c>
+      <x:c r="D16" s="14" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="str">
+        <x:v>ไม่มี business localStorage/mock fallback</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="28" customHeight="1">
+      <x:c r="A17" s="14" t="str">
+        <x:v>OUT OF SCOPE</x:v>
+      </x:c>
+      <x:c r="B17" s="14" t="str">
+        <x:v>Were OK / Work Permit</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="str">
+        <x:v>เมนูถูกปิดใน menu config</x:v>
+      </x:c>
+      <x:c r="D17" s="14" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="str">
+        <x:v>ไม่บังคับเชื่อม UI จนกว่าจะเปิดเมนู</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -804,10 +855,10 @@
         <x:v>Total API rows</x:v>
       </x:c>
       <x:c r="C1" s="9" t="str">
-        <x:v>Existing in repo</x:v>
+        <x:v>Existing/Connected</x:v>
       </x:c>
       <x:c r="D1" s="9" t="str">
-        <x:v>Target/New</x:v>
+        <x:v>Disabled menu</x:v>
       </x:c>
       <x:c r="E1" s="9" t="str">
         <x:v>Comment</x:v>
@@ -818,16 +869,16 @@
         <x:v>Safety Culture</x:v>
       </x:c>
       <x:c r="B2" s="4" t="n">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C2" s="4" t="n">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D2" s="4" t="n">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E2" s="4" t="str">
-        <x:v>target design สำหรับ implement</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -844,7 +895,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E3" s="4" t="str">
-        <x:v>Plant ใช้ CPAC mirror; RMR read-only และ Admin editable</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -855,13 +906,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="4" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D4" s="4" t="n">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="E4" s="4" t="str">
-        <x:v>target design สำหรับ implement</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -872,64 +923,64 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C5" s="4" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D5" s="4" t="n">
-        <x:v>9</x:v>
-      </x:c>
       <x:c r="E5" s="4" t="str">
-        <x:v>target design สำหรับ implement</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="4" t="str">
-        <x:v>Check-in</x:v>
+        <x:v>Assessment</x:v>
       </x:c>
       <x:c r="B6" s="4" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="4" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D6" s="4" t="n">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E6" s="4" t="str">
-        <x:v>target design สำหรับ implement</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="4" t="str">
-        <x:v>Safety Effort</x:v>
+        <x:v>Check-in</x:v>
       </x:c>
       <x:c r="B7" s="4" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D7" s="4" t="n">
-        <x:v>7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
-        <x:v>มีบางเส้นแล้วใน repo และมี target เพิ่ม</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="4" t="str">
-        <x:v>Assessment</x:v>
+        <x:v>Safety Effort</x:v>
       </x:c>
       <x:c r="B8" s="4" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C8" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D8" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D8" s="4" t="n">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="E8" s="4" t="str">
-        <x:v>target design สำหรับ implement</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -940,13 +991,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C9" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D9" s="4" t="n">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="E9" s="4" t="str">
-        <x:v>target design สำหรับ implement</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -957,30 +1008,30 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C10" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D10" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D10" s="4" t="n">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="E10" s="4" t="str">
-        <x:v>target design สำหรับ implement</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="4" t="str">
-        <x:v>Organizations</x:v>
+        <x:v>Corrective Action</x:v>
       </x:c>
       <x:c r="B11" s="4" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C11" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D11" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D11" s="4" t="n">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>target design สำหรับ implement</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -991,115 +1042,115 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C12" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D12" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D12" s="4" t="n">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="E12" s="4" t="str">
-        <x:v>target design สำหรับ implement</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="4" t="str">
-        <x:v>Corrective Action</x:v>
+        <x:v>Organizations</x:v>
       </x:c>
       <x:c r="B13" s="4" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C13" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D13" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D13" s="4" t="n">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="E13" s="4" t="str">
-        <x:v>target design สำหรับ implement</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="4" t="str">
-        <x:v>Safety Culture Admin</x:v>
+        <x:v>Rewards Admin</x:v>
       </x:c>
       <x:c r="B14" s="4" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C14" s="4" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D14" s="4" t="n">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
-        <x:v>target design สำหรับ implement</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="4" t="str">
-        <x:v>Rewards Admin</x:v>
+        <x:v>Safety Culture Admin</x:v>
       </x:c>
       <x:c r="B15" s="4" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C15" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D15" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D15" s="4" t="n">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="E15" s="4" t="str">
-        <x:v>target design สำหรับ implement</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="4" t="str">
-        <x:v>Uploads</x:v>
+        <x:v>Awareness Admin</x:v>
       </x:c>
       <x:c r="B16" s="4" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C16" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D16" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D16" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="E16" s="4" t="str">
-        <x:v>target design สำหรับ implement</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="4" t="str">
-        <x:v>Awareness Admin</x:v>
+        <x:v>Media</x:v>
       </x:c>
       <x:c r="B17" s="4" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C17" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D17" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D17" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>target design สำหรับ implement</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="4" t="str">
-        <x:v>Media</x:v>
+        <x:v>Uploads</x:v>
       </x:c>
       <x:c r="B18" s="4" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C18" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D18" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D18" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="E18" s="4" t="str">
-        <x:v>target design สำหรับ implement</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1116,7 +1167,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>มีบางเส้นแล้วใน repo และมี target เพิ่ม</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1133,7 +1184,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>target design สำหรับ implement</x:v>
+        <x:v>Backend route คงไว้ แต่เมนูปิดและไม่เชื่อม production UI</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1144,13 +1195,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C21" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D21" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D21" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="E21" s="4" t="str">
-        <x:v>target design สำหรับ implement</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1161,18 +1212,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C22" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D22" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
-        <x:v>target design สำหรับ implement</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="4" t="str">
-        <x:v>System</x:v>
+        <x:v>Settings</x:v>
       </x:c>
       <x:c r="B23" s="4" t="n">
         <x:v>2</x:v>
@@ -1184,41 +1235,41 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>target design สำหรับ implement</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="4" t="str">
-        <x:v>Assistant</x:v>
+        <x:v>System</x:v>
       </x:c>
       <x:c r="B24" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C24" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D24" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
-        <x:v>มีบางเส้นแล้วใน repo และมี target เพิ่ม</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="4" t="str">
-        <x:v>Awareness</x:v>
+        <x:v>Assistant</x:v>
       </x:c>
       <x:c r="B25" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C25" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D25" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D25" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E25" s="4" t="str">
-        <x:v>target design สำหรับ implement</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1229,30 +1280,47 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C26" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D26" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D26" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E26" s="4" t="str">
-        <x:v>target design สำหรับ implement</x:v>
+        <x:v>API implementation มีใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="4" t="str">
+        <x:v>Awareness</x:v>
+      </x:c>
+      <x:c r="B27" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C27" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D27" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E27" s="4" t="str">
+        <x:v>API implementation มีใน repo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="28" customHeight="1">
+      <x:c r="A28" s="14" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B27" s="4" t="n">
+      <x:c r="B28" s="14" t="n">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="n">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="C27" s="4" t="n">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D27" s="4" t="n">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="E27" s="4" t="str">
-        <x:v>จำนวนเส้นใน inventory sheet</x:v>
+      <x:c r="D28" s="14" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E28" s="14" t="str">
+        <x:v>159 routes; active-menu routes connected</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1344,7 +1412,7 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K2" s="4" t="str">
-        <x:v>มี implementation ใน repo</x:v>
+        <x:v>มีแล้วใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1379,7 +1447,7 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K3" s="4" t="str">
-        <x:v>มี implementation ใน repo</x:v>
+        <x:v>มีแล้วใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1414,7 +1482,7 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K4" s="4" t="str">
-        <x:v>มี implementation ใน repo</x:v>
+        <x:v>มีแล้วใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1434,7 +1502,7 @@
         <x:v>Header/Profile</x:v>
       </x:c>
       <x:c r="F5" s="4" t="str">
-        <x:v>เมื่อผู้ใช้เปิด logout endpoint</x:v>
+        <x:v>เมื่อกด logout</x:v>
       </x:c>
       <x:c r="G5" s="4" t="str">
         <x:v>User</x:v>
@@ -1449,7 +1517,7 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K5" s="4" t="str">
-        <x:v>มี dedicated route และล้าง session cookie</x:v>
+        <x:v>มีแล้วใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1484,7 +1552,7 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K6" s="4" t="str">
-        <x:v>มี implementation ใน repo</x:v>
+        <x:v>มีแล้วใน repo</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1498,7 +1566,7 @@
         <x:v>/api/locations/plants</x:v>
       </x:c>
       <x:c r="D7" s="4" t="str">
-        <x:v>รายการโรงงานจาก CPAC mirror รวม RMR SSO Plant และ Admin Plant</x:v>
+        <x:v>รายการโรงงานสำหรับ check-in/search</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
         <x:v>Check-in, Admin</x:v>
@@ -1519,7 +1587,7 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K7" s="4" t="str">
-        <x:v>อ่าน CPAC locations; คืน source, externalKey, readOnly; ไม่ query rmr_sso ทุก request</x:v>
+        <x:v>แยกจาก all locations เพราะข้อมูลเยอะ</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1743,7 +1811,7 @@
         <x:v>/api/locations</x:v>
       </x:c>
       <x:c r="D14" s="4" t="str">
-        <x:v>เพิ่ม location; ถ้า type=PLANT บังคับ source=ADMIN</x:v>
+        <x:v>เพิ่ม location ใหม่</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
         <x:v>Admin</x:v>
@@ -1764,7 +1832,7 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K14" s="4" t="str">
-        <x:v>เขียน CPAC_Safety.locations; Plant Admin ไม่เขียนกลับ rmr_sso.Plant</x:v>
+        <x:v>เขียนลง locations</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1778,7 +1846,7 @@
         <x:v>/api/locations/:id</x:v>
       </x:c>
       <x:c r="D15" s="4" t="str">
-        <x:v>แก้ไข location ที่ source อนุญาต</x:v>
+        <x:v>แก้ไข location</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
         <x:v>Admin</x:v>
@@ -1799,7 +1867,7 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K15" s="4" t="str">
-        <x:v>อนุญาต ADMIN/USER ตามสิทธิ์; RMR_SSO_PLANT ต้องตอบ 403 source_read_only</x:v>
+        <x:v>ต้อง audit</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1813,7 +1881,7 @@
         <x:v>/api/locations/:id</x:v>
       </x:c>
       <x:c r="D16" s="4" t="str">
-        <x:v>soft delete location ที่ source อนุญาต</x:v>
+        <x:v>soft delete location</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
         <x:v>Admin</x:v>
@@ -1834,7 +1902,7 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K16" s="4" t="str">
-        <x:v>อนุญาต ADMIN/USER ตามสิทธิ์; RMR_SSO_PLANT ต้องตอบ 403 source_read_only</x:v>
+        <x:v>soft delete เท่านั้น</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -2216,7 +2284,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J27" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K27" s="4" t="str">
         <x:v>สร้าง safety_activities</x:v>
@@ -2251,7 +2319,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J28" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K28" s="4" t="str">
         <x:v>ใช้ resume draft/submitted</x:v>
@@ -2286,7 +2354,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J29" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K29" s="4" t="str">
         <x:v>เชื่อม checkin</x:v>
@@ -2321,7 +2389,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J30" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K30" s="4" t="str">
         <x:v>status draft/submitted/cancelled</x:v>
@@ -2356,7 +2424,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J31" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K31" s="4" t="str">
         <x:v>cache ได้</x:v>
@@ -2391,7 +2459,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J32" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K32" s="4" t="str">
         <x:v>payload ไม่ฝัง base64</x:v>
@@ -2426,7 +2494,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J33" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K33" s="4" t="str">
         <x:v>รวม answers + media refs</x:v>
@@ -2461,7 +2529,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="J34" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K34" s="4" t="str">
         <x:v>export แยก endpoint</x:v>
@@ -2496,7 +2564,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="J35" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K35" s="4" t="str">
         <x:v>สำหรับไฟล์ใหญ่ควรใช้ async job</x:v>
@@ -2531,7 +2599,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J36" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K36" s="4" t="str">
         <x:v>แยก finding จาก answer ถ้าต้อง track action</x:v>
@@ -2566,7 +2634,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J37" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K37" s="4" t="str">
         <x:v>ผูก safety_findings</x:v>
@@ -2601,7 +2669,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J38" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K38" s="4" t="str">
         <x:v>dashboard action</x:v>
@@ -2621,10 +2689,10 @@
         <x:v>บันทึก Fit to Drive/health check</x:v>
       </x:c>
       <x:c r="E39" s="4" t="str">
-        <x:v>Were OK</x:v>
+        <x:v>เมนูปิดอยู่</x:v>
       </x:c>
       <x:c r="F39" s="4" t="str">
-        <x:v>หลัง submit</x:v>
+        <x:v>ไม่เรียกจาก production UI</x:v>
       </x:c>
       <x:c r="G39" s="4" t="str">
         <x:v>User</x:v>
@@ -2636,10 +2704,10 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J39" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Disabled</x:v>
       </x:c>
       <x:c r="K39" s="4" t="str">
-        <x:v>รูป BP/Alc ใช้ uploads</x:v>
+        <x:v>Backend route คงไว้ แต่ /were-ok ถูกปิดใน menu config และไม่อยู่ใน scope การเชื่อม UI</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -2656,10 +2724,10 @@
         <x:v>บันทึก Pre-trip Check</x:v>
       </x:c>
       <x:c r="E40" s="4" t="str">
-        <x:v>Were OK</x:v>
+        <x:v>เมนูปิดอยู่</x:v>
       </x:c>
       <x:c r="F40" s="4" t="str">
-        <x:v>หลัง submit</x:v>
+        <x:v>ไม่เรียกจาก production UI</x:v>
       </x:c>
       <x:c r="G40" s="4" t="str">
         <x:v>User</x:v>
@@ -2671,10 +2739,10 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J40" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Disabled</x:v>
       </x:c>
       <x:c r="K40" s="4" t="str">
-        <x:v>payload JSON + activityId</x:v>
+        <x:v>Backend route คงไว้ แต่ /were-ok ถูกปิดใน menu config และไม่อยู่ใน scope การเชื่อม UI</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -2691,10 +2759,10 @@
         <x:v>บันทึก KYT</x:v>
       </x:c>
       <x:c r="E41" s="4" t="str">
-        <x:v>Were OK</x:v>
+        <x:v>เมนูปิดอยู่</x:v>
       </x:c>
       <x:c r="F41" s="4" t="str">
-        <x:v>หลัง submit</x:v>
+        <x:v>ไม่เรียกจาก production UI</x:v>
       </x:c>
       <x:c r="G41" s="4" t="str">
         <x:v>User</x:v>
@@ -2706,10 +2774,10 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J41" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Disabled</x:v>
       </x:c>
       <x:c r="K41" s="4" t="str">
-        <x:v>รูป KYT ใช้ uploads</x:v>
+        <x:v>Backend route คงไว้ แต่ /were-ok ถูกปิดใน menu config และไม่อยู่ใน scope การเชื่อม UI</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -2726,10 +2794,10 @@
         <x:v>บันทึก SOS</x:v>
       </x:c>
       <x:c r="E42" s="4" t="str">
-        <x:v>Were OK</x:v>
+        <x:v>เมนูปิดอยู่</x:v>
       </x:c>
       <x:c r="F42" s="4" t="str">
-        <x:v>หลัง submit</x:v>
+        <x:v>ไม่เรียกจาก production UI</x:v>
       </x:c>
       <x:c r="G42" s="4" t="str">
         <x:v>User</x:v>
@@ -2741,10 +2809,10 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J42" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Disabled</x:v>
       </x:c>
       <x:c r="K42" s="4" t="str">
-        <x:v>แจ้งเตือน admin</x:v>
+        <x:v>Backend route คงไว้ แต่ /were-ok ถูกปิดใน menu config และไม่อยู่ใน scope การเชื่อม UI</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -3091,7 +3159,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J52" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K52" s="4" t="str">
         <x:v>live/scheduled/closed</x:v>
@@ -3126,7 +3194,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J53" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K53" s="4" t="str">
         <x:v>แทน localStorage</x:v>
@@ -3161,7 +3229,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J54" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K54" s="4" t="str">
         <x:v>audit</x:v>
@@ -3196,7 +3264,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J55" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K55" s="4" t="str">
         <x:v>cache รายช่วงเวลา</x:v>
@@ -3231,7 +3299,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J56" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K56" s="4" t="str">
         <x:v>cache ได้</x:v>
@@ -3266,7 +3334,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J57" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K57" s="4" t="str">
         <x:v>transactional</x:v>
@@ -3301,7 +3369,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J58" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K58" s="4" t="str">
         <x:v>cache by date</x:v>
@@ -3371,7 +3439,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J60" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K60" s="4" t="str">
         <x:v>แทน in-memory/localStorage</x:v>
@@ -3406,9 +3474,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J61" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K61" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K61" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="4" t="str">
@@ -3439,7 +3509,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J62" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K62" s="4" t="str">
         <x:v>อาจ queue</x:v>
@@ -3474,7 +3544,7 @@
         <x:v>Upload size limit</x:v>
       </x:c>
       <x:c r="J63" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K63" s="4" t="str">
         <x:v>multipart/form-data</x:v>
@@ -3509,7 +3579,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J64" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K64" s="4" t="str">
         <x:v>ตรวจสิทธิ์</x:v>
@@ -3544,7 +3614,7 @@
         <x:v>File</x:v>
       </x:c>
       <x:c r="J65" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K65" s="4" t="str">
         <x:v>ใช้ signed URL/private URL</x:v>
@@ -3579,7 +3649,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J66" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K66" s="4" t="str">
         <x:v>soft delete + object lifecycle</x:v>
@@ -3614,7 +3684,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J67" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K67" s="4" t="str">
         <x:v>ลบรูปที่ไม่ถูกผูกกับ owner</x:v>
@@ -3649,7 +3719,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J68" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K68" s="4" t="str">
         <x:v>ใช้กับ company/division/fact/section</x:v>
@@ -3684,7 +3754,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J69" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K69" s="4" t="str">
         <x:v>ไม่โหลด tree ใหญ่ทุกครั้ง</x:v>
@@ -3719,9 +3789,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J70" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K70" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K70" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="4" t="str">
@@ -3752,7 +3824,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J71" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K71" s="4" t="str">
         <x:v>audit required</x:v>
@@ -3787,7 +3859,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J72" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K72" s="4" t="str">
         <x:v>audit required</x:v>
@@ -3822,7 +3894,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J73" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K73" s="4" t="str">
         <x:v>ต้องตรวจ child ก่อนลบ</x:v>
@@ -3857,7 +3929,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J74" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K74" s="4" t="str">
         <x:v>merge SSO + app profile</x:v>
@@ -3892,7 +3964,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J75" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K75" s="4" t="str">
         <x:v>profile image ใช้ mediaId</x:v>
@@ -3927,7 +3999,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J76" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K76" s="4" t="str">
         <x:v>ต้อง limit search</x:v>
@@ -3962,9 +4034,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J77" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K77" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K77" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="4" t="str">
@@ -3995,7 +4069,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J78" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K78" s="4" t="str">
         <x:v>audit required</x:v>
@@ -4030,9 +4104,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J79" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K79" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K79" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="4" t="str">
@@ -4063,9 +4139,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J80" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K80" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K80" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="4" t="str">
@@ -4096,9 +4174,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J81" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K81" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K81" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="4" t="str">
@@ -4129,9 +4209,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J82" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K82" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K82" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="4" t="str">
@@ -4162,7 +4244,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J83" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K83" s="4" t="str">
         <x:v>transactional</x:v>
@@ -4197,7 +4279,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J84" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K84" s="4" t="str">
         <x:v>transactional</x:v>
@@ -4214,13 +4296,13 @@
         <x:v>/api/location-imports</x:v>
       </x:c>
       <x:c r="D85" s="4" t="str">
-        <x:v>เริ่ม import/sync location master</x:v>
+        <x:v>upload/import master location file</x:v>
       </x:c>
       <x:c r="E85" s="4" t="str">
-        <x:v>Admin/Scheduled job</x:v>
+        <x:v>Admin</x:v>
       </x:c>
       <x:c r="F85" s="4" t="str">
-        <x:v>Admin import หรือ incremental RMR Plant sync</x:v>
+        <x:v>admin import DataOcean/Excel</x:v>
       </x:c>
       <x:c r="G85" s="4" t="str">
         <x:v>Admin</x:v>
@@ -4232,10 +4314,10 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="J85" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K85" s="4" t="str">
-        <x:v>รองรับ body {source:"RMR_SSO_PLANT"}; SELECT-only แล้ว upsert CPAC mirror</x:v>
+        <x:v>สร้าง batch</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -4267,9 +4349,11 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J86" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K86" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K86" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="4" t="str">
@@ -4300,7 +4384,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J87" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K87" s="4" t="str">
         <x:v>รวม summary success/fail</x:v>
@@ -4335,7 +4419,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="J88" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K88" s="4" t="str">
         <x:v>จำเป็นต้องแบ่งหน้า</x:v>
@@ -4370,9 +4454,11 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J89" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K89" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K89" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="4" t="str">
@@ -4403,7 +4489,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="J90" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K90" s="4" t="str">
         <x:v>upsert locations</x:v>
@@ -4438,7 +4524,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J91" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K91" s="4" t="str">
         <x:v>spatial distance query</x:v>
@@ -4473,7 +4559,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J92" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K92" s="4" t="str">
         <x:v>ใช้ attachmentIds</x:v>
@@ -4508,9 +4594,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J93" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K93" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K93" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="4" t="str">
@@ -4541,7 +4629,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J94" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K94" s="4" t="str">
         <x:v>ใช้ aggregate/cache</x:v>
@@ -4576,9 +4664,11 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J95" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K95" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K95" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="4" t="str">
@@ -4609,7 +4699,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J96" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K96" s="4" t="str">
         <x:v>versioned</x:v>
@@ -4644,9 +4734,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J97" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K97" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K97" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="4" t="str">
@@ -4677,7 +4769,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J98" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K98" s="4" t="str">
         <x:v>lock questions</x:v>
@@ -4712,9 +4804,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J99" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K99" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K99" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="4" t="str">
@@ -4745,9 +4839,11 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J100" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K100" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K100" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="4" t="str">
@@ -4778,9 +4874,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J101" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K101" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K101" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="4" t="str">
@@ -4811,9 +4909,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J102" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K102" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K102" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="4" t="str">
@@ -4844,7 +4944,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J103" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K103" s="4" t="str">
         <x:v>soft disable if published</x:v>
@@ -4879,7 +4979,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J104" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K104" s="4" t="str">
         <x:v>server validates complete answers</x:v>
@@ -4914,7 +5014,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J105" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K105" s="4" t="str">
         <x:v>attachmentIds only</x:v>
@@ -4949,9 +5049,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J106" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K106" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K106" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="4" t="str">
@@ -4982,7 +5084,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J107" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K107" s="4" t="str">
         <x:v>cache by filter</x:v>
@@ -5017,9 +5119,11 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="J108" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K108" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K108" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="4" t="str">
@@ -5050,9 +5154,11 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="J109" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K109" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K109" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="4" t="str">
@@ -5083,9 +5189,11 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="J110" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K110" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K110" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="4" t="str">
@@ -5116,7 +5224,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="J111" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K111" s="4" t="str">
         <x:v>ใช้ได้หลาย module</x:v>
@@ -5151,9 +5259,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J112" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K112" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K112" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="4" t="str">
@@ -5184,7 +5294,7 @@
         <x:v>File</x:v>
       </x:c>
       <x:c r="J113" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K113" s="4" t="str">
         <x:v>signed URL or stream</x:v>
@@ -5219,9 +5329,11 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="J114" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K114" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K114" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="4" t="str">
@@ -5252,7 +5364,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J115" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K115" s="4" t="str">
         <x:v>รวม action/media</x:v>
@@ -5287,9 +5399,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J116" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K116" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K116" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="4" t="str">
@@ -5320,9 +5434,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J117" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K117" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K117" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="4" t="str">
@@ -5353,7 +5469,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J118" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K118" s="4" t="str">
         <x:v>require evidence optional</x:v>
@@ -5388,9 +5504,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J119" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K119" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K119" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="4" t="str">
@@ -5421,9 +5539,11 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="J120" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K120" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K120" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="4" t="str">
@@ -5454,7 +5574,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J121" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K121" s="4" t="str">
         <x:v>optional if moderation enabled</x:v>
@@ -5489,7 +5609,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J122" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K122" s="4" t="str">
         <x:v>with reason</x:v>
@@ -5524,9 +5644,11 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J123" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K123" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K123" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="4" t="str">
@@ -5557,9 +5679,11 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J124" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K124" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K124" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="4" t="str">
@@ -5593,7 +5717,7 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K125" s="4" t="str">
-        <x:v>มี implementation ใน repo</x:v>
+        <x:v>DB-backed implementation</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -5628,7 +5752,7 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K126" s="4" t="str">
-        <x:v>มี implementation ใน repo</x:v>
+        <x:v>DB-backed implementation</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -5663,7 +5787,7 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K127" s="4" t="str">
-        <x:v>มี implementation ใน repo</x:v>
+        <x:v>DB-backed implementation</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -5695,7 +5819,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J128" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K128" s="4" t="str">
         <x:v>audit required</x:v>
@@ -5765,7 +5889,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J130" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K130" s="4" t="str">
         <x:v>reward image mediaId</x:v>
@@ -5800,9 +5924,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J131" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K131" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K131" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="4" t="str">
@@ -5833,7 +5959,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J132" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K132" s="4" t="str">
         <x:v>soft delete</x:v>
@@ -5868,9 +5994,11 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="J133" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K133" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K133" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="4" t="str">
@@ -5901,7 +6029,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J134" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K134" s="4" t="str">
         <x:v>transaction-safe</x:v>
@@ -5936,7 +6064,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J135" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K135" s="4" t="str">
         <x:v>ledger</x:v>
@@ -5971,9 +6099,11 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J136" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K136" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K136" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="4" t="str">
@@ -6004,9 +6134,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J137" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K137" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K137" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="4" t="str">
@@ -6037,9 +6169,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J138" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K138" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K138" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="4" t="str">
@@ -6070,7 +6204,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J139" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K139" s="4" t="str">
         <x:v>soft disable</x:v>
@@ -6105,9 +6239,11 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J140" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K140" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K140" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="4" t="str">
@@ -6138,9 +6274,11 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="J141" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K141" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K141" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="4" t="str">
@@ -6171,7 +6309,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J142" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K142" s="4" t="str">
         <x:v>cache yearly</x:v>
@@ -6206,9 +6344,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J143" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K143" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K143" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="4" t="str">
@@ -6239,9 +6379,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J144" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K144" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K144" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="4" t="str">
@@ -6272,9 +6414,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J145" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K145" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K145" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="4" t="str">
@@ -6305,9 +6449,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J146" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K146" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K146" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="4" t="str">
@@ -6338,9 +6484,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J147" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K147" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K147" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="4" t="str">
@@ -6371,9 +6519,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J148" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K148" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K148" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="4" t="str">
@@ -6404,7 +6554,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J149" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K149" s="4" t="str">
         <x:v>ownerType/ownerId/linkType</x:v>
@@ -6439,9 +6589,11 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J150" s="10" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="K150" s="4"/>
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K150" s="4" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="4" t="str">
@@ -6472,7 +6624,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="J151" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K151" s="4" t="str">
         <x:v>ตรวจสิทธิ์ตาม owner</x:v>
@@ -6507,7 +6659,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J152" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K152" s="4" t="str">
         <x:v>optional for scale</x:v>
@@ -6542,7 +6694,7 @@
         <x:v>Small</x:v>
       </x:c>
       <x:c r="J153" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K153" s="4" t="str">
         <x:v>verify object exists</x:v>
@@ -6550,60 +6702,60 @@
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="4" t="str">
-        <x:v>Audit</x:v>
+        <x:v>Safety Culture</x:v>
       </x:c>
       <x:c r="B154" s="4" t="str">
         <x:v>GET</x:v>
       </x:c>
       <x:c r="C154" s="4" t="str">
-        <x:v>/api/audit-logs?actor=&amp;entity=&amp;from=&amp;to=&amp;page=&amp;pageSize=</x:v>
+        <x:v>/api/safety-culture/teams</x:v>
       </x:c>
       <x:c r="D154" s="4" t="str">
-        <x:v>audit trail</x:v>
+        <x:v>อ่านทีมสำหรับหน้า admin leaderboard</x:v>
       </x:c>
       <x:c r="E154" s="4" t="str">
-        <x:v>Admin/Security</x:v>
+        <x:v>Admin Leaderboard</x:v>
       </x:c>
       <x:c r="F154" s="4" t="str">
-        <x:v>ตรวจสอบการแก้ไข</x:v>
+        <x:v>เปิดหน้าจัดการทีม</x:v>
       </x:c>
       <x:c r="G154" s="4" t="str">
-        <x:v>Admin</x:v>
+        <x:v>User</x:v>
       </x:c>
       <x:c r="H154" s="4" t="str">
-        <x:v>Required</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="I154" s="4" t="str">
-        <x:v>High</x:v>
+        <x:v>Small</x:v>
       </x:c>
       <x:c r="J154" s="10" t="str">
-        <x:v>Target</x:v>
+        <x:v>Existing</x:v>
       </x:c>
       <x:c r="K154" s="4" t="str">
-        <x:v>ห้ามเปิด public</x:v>
+        <x:v>อ่านจาก teams และ team_members</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="4" t="str">
-        <x:v>System</x:v>
+        <x:v>Safety Culture</x:v>
       </x:c>
       <x:c r="B155" s="4" t="str">
-        <x:v>GET</x:v>
+        <x:v>PUT</x:v>
       </x:c>
       <x:c r="C155" s="4" t="str">
-        <x:v>/api/health</x:v>
+        <x:v>/api/safety-culture/teams</x:v>
       </x:c>
       <x:c r="D155" s="4" t="str">
-        <x:v>health check</x:v>
+        <x:v>บันทึกรายการทีมสำหรับ leaderboard</x:v>
       </x:c>
       <x:c r="E155" s="4" t="str">
-        <x:v>Infra</x:v>
+        <x:v>Admin Leaderboard</x:v>
       </x:c>
       <x:c r="F155" s="4" t="str">
-        <x:v>monitoring</x:v>
+        <x:v>เมื่อ admin บันทึกทีม</x:v>
       </x:c>
       <x:c r="G155" s="4" t="str">
-        <x:v>Public/Internal</x:v>
+        <x:v>Admin</x:v>
       </x:c>
       <x:c r="H155" s="4" t="str">
         <x:v>No</x:v>
@@ -6615,42 +6767,182 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K155" s="4" t="str">
-        <x:v>มี implementation ใน repo</x:v>
+        <x:v>upsert/soft-delete teams</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="4" t="str">
-        <x:v>System</x:v>
+        <x:v>Settings</x:v>
       </x:c>
       <x:c r="B156" s="4" t="str">
         <x:v>GET</x:v>
       </x:c>
       <x:c r="C156" s="4" t="str">
+        <x:v>/api/safety-settings?key=</x:v>
+      </x:c>
+      <x:c r="D156" s="4" t="str">
+        <x:v>อ่านค่า safety settings จากฐานจริง</x:v>
+      </x:c>
+      <x:c r="E156" s="4" t="str">
+        <x:v>Safety Admin/DatePicker</x:v>
+      </x:c>
+      <x:c r="F156" s="4" t="str">
+        <x:v>โหลดหน้าหรือเปิด setting</x:v>
+      </x:c>
+      <x:c r="G156" s="4" t="str">
+        <x:v>User</x:v>
+      </x:c>
+      <x:c r="H156" s="4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I156" s="4" t="str">
+        <x:v>Small</x:v>
+      </x:c>
+      <x:c r="J156" s="10" t="str">
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K156" s="4" t="str">
+        <x:v>ใช้ safety_settings ไม่ใช้ localStorage</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="28" customHeight="1">
+      <x:c r="A157" s="14" t="str">
+        <x:v>Settings</x:v>
+      </x:c>
+      <x:c r="B157" s="14" t="str">
+        <x:v>PUT</x:v>
+      </x:c>
+      <x:c r="C157" s="14" t="str">
+        <x:v>/api/safety-settings</x:v>
+      </x:c>
+      <x:c r="D157" s="14" t="str">
+        <x:v>บันทึกค่า safety settings ลงฐานจริง</x:v>
+      </x:c>
+      <x:c r="E157" s="14" t="str">
+        <x:v>Safety Admin</x:v>
+      </x:c>
+      <x:c r="F157" s="14" t="str">
+        <x:v>เมื่อ admin save settings</x:v>
+      </x:c>
+      <x:c r="G157" s="14" t="str">
+        <x:v>Admin</x:v>
+      </x:c>
+      <x:c r="H157" s="14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I157" s="14" t="str">
+        <x:v>Small</x:v>
+      </x:c>
+      <x:c r="J157" s="14" t="str">
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K157" s="14" t="str">
+        <x:v>upsert safety_settings</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="28" customHeight="1">
+      <x:c r="A158" s="14" t="str">
+        <x:v>Audit</x:v>
+      </x:c>
+      <x:c r="B158" s="14" t="str">
+        <x:v>GET</x:v>
+      </x:c>
+      <x:c r="C158" s="14" t="str">
+        <x:v>/api/audit-logs?actor=&amp;entity=&amp;from=&amp;to=&amp;page=&amp;pageSize=</x:v>
+      </x:c>
+      <x:c r="D158" s="14" t="str">
+        <x:v>audit trail</x:v>
+      </x:c>
+      <x:c r="E158" s="14" t="str">
+        <x:v>Admin/Security</x:v>
+      </x:c>
+      <x:c r="F158" s="14" t="str">
+        <x:v>ตรวจสอบการแก้ไข</x:v>
+      </x:c>
+      <x:c r="G158" s="14" t="str">
+        <x:v>Admin</x:v>
+      </x:c>
+      <x:c r="H158" s="14" t="str">
+        <x:v>Required</x:v>
+      </x:c>
+      <x:c r="I158" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="J158" s="14" t="str">
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K158" s="14" t="str">
+        <x:v>ห้ามเปิด public</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="28" customHeight="1">
+      <x:c r="A159" s="14" t="str">
+        <x:v>System</x:v>
+      </x:c>
+      <x:c r="B159" s="14" t="str">
+        <x:v>GET</x:v>
+      </x:c>
+      <x:c r="C159" s="14" t="str">
+        <x:v>/api/health</x:v>
+      </x:c>
+      <x:c r="D159" s="14" t="str">
+        <x:v>health check</x:v>
+      </x:c>
+      <x:c r="E159" s="14" t="str">
+        <x:v>Infra</x:v>
+      </x:c>
+      <x:c r="F159" s="14" t="str">
+        <x:v>monitoring</x:v>
+      </x:c>
+      <x:c r="G159" s="14" t="str">
+        <x:v>Public/Internal</x:v>
+      </x:c>
+      <x:c r="H159" s="14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I159" s="14" t="str">
+        <x:v>Small</x:v>
+      </x:c>
+      <x:c r="J159" s="14" t="str">
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K159" s="14" t="str">
+        <x:v>DB-backed implementation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="28" customHeight="1">
+      <x:c r="A160" s="14" t="str">
+        <x:v>System</x:v>
+      </x:c>
+      <x:c r="B160" s="14" t="str">
+        <x:v>GET</x:v>
+      </x:c>
+      <x:c r="C160" s="14" t="str">
         <x:v>/api/version</x:v>
       </x:c>
-      <x:c r="D156" s="4" t="str">
+      <x:c r="D160" s="14" t="str">
         <x:v>app/api version</x:v>
       </x:c>
-      <x:c r="E156" s="4" t="str">
+      <x:c r="E160" s="14" t="str">
         <x:v>Infra/Debug</x:v>
       </x:c>
-      <x:c r="F156" s="4" t="str">
+      <x:c r="F160" s="14" t="str">
         <x:v>debug</x:v>
       </x:c>
-      <x:c r="G156" s="4" t="str">
+      <x:c r="G160" s="14" t="str">
         <x:v>Public/Internal</x:v>
       </x:c>
-      <x:c r="H156" s="4" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="I156" s="4" t="str">
-        <x:v>Small</x:v>
-      </x:c>
-      <x:c r="J156" s="10" t="str">
-        <x:v>Existing</x:v>
-      </x:c>
-      <x:c r="K156" s="4" t="str">
-        <x:v>มี implementation ใน repo</x:v>
+      <x:c r="H160" s="14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I160" s="14" t="str">
+        <x:v>Small</x:v>
+      </x:c>
+      <x:c r="J160" s="14" t="str">
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K160" s="14" t="str">
+        <x:v>DB-backed implementation</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7239,7 +7531,7 @@
         <x:v>feed posts</x:v>
       </x:c>
       <x:c r="D2" s="4" t="str">
-        <x:v>posts, users, reactions, comments summary, media_asset_links</x:v>
+        <x:v>posts, users, reactions, comments summary, media_assets(owner_type, owner_id, link_type)</x:v>
       </x:c>
       <x:c r="E2" s="4" t="str">
         <x:v>cursor+limit</x:v>
@@ -7248,7 +7540,7 @@
         <x:v>thumbnail URLs only</x:v>
       </x:c>
       <x:c r="G2" s="4" t="str">
-        <x:v>แทน localStorage</x:v>
+        <x:v>อ่านจากฐานจริง; API fail แสดง error/empty state</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -7262,7 +7554,7 @@
         <x:v>create post</x:v>
       </x:c>
       <x:c r="D3" s="4" t="str">
-        <x:v>posts, media_asset_links, point_transactions</x:v>
+        <x:v>posts, media_assets(owner_type, owner_id, link_type), point_transactions</x:v>
       </x:c>
       <x:c r="E3" s="4" t="str">
         <x:v>none</x:v>
@@ -7354,7 +7646,7 @@
         <x:v>campaign/activity config</x:v>
       </x:c>
       <x:c r="D7" s="4" t="str">
-        <x:v>culture_events</x:v>
+        <x:v>safety_safety_culture_events</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
         <x:v>page for admin</x:v>
@@ -7490,16 +7782,16 @@
         <x:v>Database</x:v>
       </x:c>
       <x:c r="B3" s="4" t="str">
-        <x:v>เก็บ metadata</x:v>
+        <x:v>เก็บ metadata และ owner link ใน media_assets</x:v>
       </x:c>
       <x:c r="C3" s="4" t="str">
-        <x:v>media_assets + media_asset_links</x:v>
+        <x:v>ใช้ owner_type, owner_id, link_type</x:v>
       </x:c>
       <x:c r="D3" s="4" t="str">
         <x:v>ค้น/ผูก owner ได้โดยไม่แตะไฟล์ใหญ่</x:v>
       </x:c>
       <x:c r="E3" s="4" t="str">
-        <x:v>id, url/key, mime, size, checksum, owner/link</x:v>
+        <x:v>ไม่มี media_asset_links แยกใน schema ปัจจุบัน</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -8011,6 +8303,142 @@
         <x:v>incremental upsert by source + external_key; missing source rows become INACTIVE</x:v>
       </x:c>
     </x:row>
+    <x:row r="22" ht="28" customHeight="1">
+      <x:c r="A22" s="14" t="str">
+        <x:v>/api/safety-culture/events</x:v>
+      </x:c>
+      <x:c r="B22" s="14" t="str">
+        <x:v>safety_culture_events</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="D22" s="14" t="str">
+        <x:v>Read/Write</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="str">
+        <x:v>กิจกรรมจริง ไม่เก็บ JSON ใน audit_logs</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="28" customHeight="1">
+      <x:c r="A23" s="14" t="str">
+        <x:v>/api/uploads, /api/media</x:v>
+      </x:c>
+      <x:c r="B23" s="14" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="D23" s="14" t="str">
+        <x:v>Read/Write</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="str">
+        <x:v>ไฟล์จริงใน storage; metadata/owner link ใน DB</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="28" customHeight="1">
+      <x:c r="A24" s="14" t="str">
+        <x:v>/api/exports</x:v>
+      </x:c>
+      <x:c r="B24" s="14" t="str">
+        <x:v>export_jobs</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="D24" s="14" t="str">
+        <x:v>Read/Write</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="str">
+        <x:v>สร้างและติดตาม export job จริง</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="28" customHeight="1">
+      <x:c r="A25" s="14" t="str">
+        <x:v>/api/notifications/preferences</x:v>
+      </x:c>
+      <x:c r="B25" s="14" t="str">
+        <x:v>notification_preferences</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="D25" s="14" t="str">
+        <x:v>Read/Write</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="str">
+        <x:v>ตั้งค่ารายผู้ใช้</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="28" customHeight="1">
+      <x:c r="A26" s="14" t="str">
+        <x:v>/api/notifications/archive</x:v>
+      </x:c>
+      <x:c r="B26" s="14" t="str">
+        <x:v>archived_notifications</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="str">
+        <x:v>notifications, users</x:v>
+      </x:c>
+      <x:c r="D26" s="14" t="str">
+        <x:v>Read/Write</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="str">
+        <x:v>เก็บ archive จริง</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="28" customHeight="1">
+      <x:c r="A27" s="14" t="str">
+        <x:v>/api/assessments/:id/attachments</x:v>
+      </x:c>
+      <x:c r="B27" s="14" t="str">
+        <x:v>assessment_attachments</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="str">
+        <x:v>assessment_runs, media_assets</x:v>
+      </x:c>
+      <x:c r="D27" s="14" t="str">
+        <x:v>Read/Write</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="str">
+        <x:v>หลักฐาน assessment</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="28" customHeight="1">
+      <x:c r="A28" s="14" t="str">
+        <x:v>/api/corrective-actions/:id/comments</x:v>
+      </x:c>
+      <x:c r="B28" s="14" t="str">
+        <x:v>corrective_action_comments</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="str">
+        <x:v>corrective_actions, users</x:v>
+      </x:c>
+      <x:c r="D28" s="14" t="str">
+        <x:v>Read/Write</x:v>
+      </x:c>
+      <x:c r="E28" s="14" t="str">
+        <x:v>ความคิดเห็น corrective action</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="28" customHeight="1">
+      <x:c r="A29" s="14" t="str">
+        <x:v>/api/safety-settings</x:v>
+      </x:c>
+      <x:c r="B29" s="14" t="str">
+        <x:v>safety_settings</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="D29" s="14" t="str">
+        <x:v>Read/Write</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="str">
+        <x:v>Admin settings จริง</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/outputs/SUEA_Safety_API_Inventory.xlsx
+++ b/outputs/SUEA_Safety_API_Inventory.xlsx
@@ -14,6 +14,8 @@
     <sheet name="08_Scale_Rules" sheetId="9" r:id="rId9"/>
     <sheet name="09_Backlog" sheetId="10" r:id="rId10"/>
     <sheet name="10_API_Counts" sheetId="11" r:id="rId11"/>
+    <sheet name="Cloudinary_Posts_QA_Update" sheetId="12" r:id="rId12"/>
+    <sheet name="Repo_Verification_2026-06-22" sheetId="13" r:id="rId13"/>
   </sheets>
 </workbook>
 </file>
@@ -590,13 +592,6 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E22"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="60.83203125" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="60.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -973,6 +968,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:E22"/>
   </ignoredErrors>
@@ -1463,6 +1459,285 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:E28"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Area</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Endpoint/Artifact</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Update</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Security/Scale Note</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Last updated</v>
+      </c>
+      <c r="G1">
+        <v>46193.118196006944</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Uploads</v>
+      </c>
+      <c r="B2" t="str">
+        <v>POST /api/uploads</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Server accepts multipart file, stores in Cloudinary when CLOUDINARY_* env is complete, then returns media DTO only.</v>
+      </c>
+      <c r="D2" t="str">
+        <v>No storage_path/provider IDs in client response; max size and MIME allow-list enforced.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Uploads</v>
+      </c>
+      <c r="B3" t="str">
+        <v>GET /api/uploads/:id</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Returns shaped media object with id/url/mime/size/status/provider only.</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Prevents raw media_assets row exposure.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Uploads</v>
+      </c>
+      <c r="B4" t="str">
+        <v>GET /api/uploads/:id/download</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Redirects to Cloudinary secure_url when present; otherwise streams local file.</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Client receives durable URL for feed images.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Safety Culture</v>
+      </c>
+      <c r="B5" t="str">
+        <v>POST /api/safety-culture/posts</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Payload: content, category, attachmentIds, feedEventId. Backend stamps author_id, organization_id, team_id, category, event_id.</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Frontend never sends trusted department/team; backend resolves from authenticated profile.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Safety Culture</v>
+      </c>
+      <c r="B6" t="str">
+        <v>GET /api/safety-culture/posts?scope=my-team&amp;cursor=&amp;limit=</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Cursor pagination by descending post id; scope=my-team filters by active team membership.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>No team returns empty items; unassigned posts stay in global feed.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>DTO</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Post response</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Includes authorName, organizationId/name, teamId/name, teamScope, category, photos[].url, counts, points.</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Excludes password hashes, internal flags, storage paths, and auth tokens.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Scalability</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Indexes</v>
+      </c>
+      <c r="C8" t="str">
+        <v>posts(status,team_id,id), posts(status,category,id), comments(post_id,deleted_at,id), media provider/status indexes.</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Ready for cursor pagination and high-volume feed/ranking queries.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>QA</v>
+      </c>
+      <c r="B9" t="str">
+        <v>npm run qa:e2e</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Playwright audit agent walks menus/buttons/uploads and fails on console error or HTTP 5xx/unexpected 4xx.</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Outputs JSON and HTML reports under test-results/playwright-report.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Cloudinary env</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Set CLOUDINARY_CLOUD_NAME, CLOUDINARY_API_KEY, CLOUDINARY_API_SECRET, CLOUDINARY_UPLOAD_FOLDER on Vercel/hosting.</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Secrets stay server-side; do not expose with NEXT_PUBLIC_.</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Topic</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Current repo status</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Source</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Verification date</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Codex audit</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>API catalog route count</v>
+      </c>
+      <c r="B3" t="str">
+        <v>174 routes currently declared in backend/components/api-catalog/registry.ts</v>
+      </c>
+      <c r="C3" t="str">
+        <v>backend/components/api-catalog/registry.ts</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Workbook drift</v>
+      </c>
+      <c r="B4" t="str">
+        <v>00_Summary still says 159 routes, so this workbook needs this verification sheet for the latest count</v>
+      </c>
+      <c r="C4" t="str">
+        <v>outputs/SUEA_Safety_API_Inventory.xlsx -&gt; 00_Summary</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Activity notification deep link</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Backend notify route stores metadata.href as /safety-culture?activityId=&lt;eventId&gt;</v>
+      </c>
+      <c r="C5" t="str">
+        <v>backend/components/api-catalog/persistence.ts</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Notification fallback behavior</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Frontend rebuilds href from postId/feedEventId/href; if old notifications were created without these fields they can still fall back to /notifications</v>
+      </c>
+      <c r="C6" t="str">
+        <v>src/providers/app-providers.tsx</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Notification timestamp UI</v>
+      </c>
+      <c r="B7" t="str">
+        <v>NotificationCenter now shows full Thai date+time instead of relative hours/minutes</v>
+      </c>
+      <c r="C7" t="str">
+        <v>src/components/notifications/notification-center.tsx</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Check-in create API</v>
+      </c>
+      <c r="B8" t="str">
+        <v>POST /api/checkins with locationId, actualLat, actualLng, actualAccuracyM, locationSource</v>
+      </c>
+      <c r="C8" t="str">
+        <v>backend/components/api-catalog/router.ts + src/features/safety-effort/screens/Checkin.tsx</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Location read APIs</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Check-in screen reads /api/locations/map and can also use /api/safety-effort/locations list endpoints</v>
+      </c>
+      <c r="C9" t="str">
+        <v>src/features/safety-effort/screens/Checkin.tsx + src/app/api/safety-effort/locations/route.ts</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Location approval flow</v>
+      </c>
+      <c r="B10" t="str">
+        <v>No approval workflow found before saving a check-in. Creating a new location uses POST /api/locations and requires admin session.</v>
+      </c>
+      <c r="C10" t="str">
+        <v>src/features/safety-effort/screens/Checkin.tsx + backend/components/api-catalog/router.ts</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7602,15 +7877,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G11"/>
-  <cols>
-    <col min="1" max="1" width="13.83203125" customWidth="1"/>
-    <col min="2" max="2" width="60.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="60.83203125" customWidth="1"/>
-    <col min="5" max="5" width="23.83203125" customWidth="1"/>
-    <col min="6" max="6" width="60.83203125" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7866,6 +8132,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:G11"/>
   </ignoredErrors>
@@ -7875,13 +8142,6 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E10"/>
-  <cols>
-    <col min="1" max="1" width="23.83203125" customWidth="1"/>
-    <col min="2" max="2" width="39.83203125" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" customWidth="1"/>
-    <col min="4" max="4" width="60.83203125" customWidth="1"/>
-    <col min="5" max="5" width="60.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8054,6 +8314,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:E10"/>
   </ignoredErrors>
@@ -8063,13 +8324,6 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E31"/>
-  <cols>
-    <col min="1" max="1" width="51.83203125" customWidth="1"/>
-    <col min="2" max="2" width="47.83203125" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" customWidth="1"/>
-    <col min="4" max="4" width="28.83203125" customWidth="1"/>
-    <col min="5" max="5" width="60.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8599,6 +8853,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:E31"/>
   </ignoredErrors>
@@ -8608,12 +8863,6 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D15"/>
-  <cols>
-    <col min="1" max="1" width="43.83203125" customWidth="1"/>
-    <col min="2" max="2" width="60.83203125" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" customWidth="1"/>
-    <col min="4" max="4" width="60.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8826,6 +9075,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:D15"/>
   </ignoredErrors>
@@ -8835,12 +9085,6 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D17"/>
-  <cols>
-    <col min="1" max="1" width="23.83203125" customWidth="1"/>
-    <col min="2" max="2" width="60.83203125" customWidth="1"/>
-    <col min="3" max="3" width="45.83203125" customWidth="1"/>
-    <col min="4" max="4" width="49.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9081,6 +9325,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:D17"/>
   </ignoredErrors>

--- a/outputs/SUEA_Safety_API_Inventory.xlsx
+++ b/outputs/SUEA_Safety_API_Inventory.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Summary" sheetId="1" r:id="R9e0cdb9376a84fba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_API_Inventory" sheetId="2" r:id="R1ed9dee9a7ec4f31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Checkin_Locations" sheetId="3" r:id="R717e6224e20a47e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Safety_Effort" sheetId="4" r:id="Rf14efc0cecad4248"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Safety_Culture" sheetId="5" r:id="R19cc6dc92a344655"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Uploads_Media" sheetId="6" r:id="R3a8a703a3f03493f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Table_Mapping" sheetId="7" r:id="R9948f0cc6964486e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Payload_Response" sheetId="8" r:id="R6754c38c42ba4158"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Scale_Rules" sheetId="9" r:id="Ra5f0c74d8ead45e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Backlog" sheetId="10" r:id="Rd41273ef9be24c0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_API_Counts" sheetId="11" r:id="Rbe45a36819f64dc0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cloudinary_Posts_QA_Update" sheetId="12" r:id="Reea572eb1327463d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Verification_2026-06-22" sheetId="13" r:id="R96fad716b6ab439c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Summary" sheetId="1" r:id="R745ff4c9f63e4c61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_API_Inventory" sheetId="2" r:id="Rd000138bda7a4ff1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Checkin_Locations" sheetId="3" r:id="R6dba5e72aaf348e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Safety_Effort" sheetId="4" r:id="R40a0fe5e514244e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Safety_Culture" sheetId="5" r:id="R33e874ac6f8d4e73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Uploads_Media" sheetId="6" r:id="Rff7dbc8ee5704fe1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Table_Mapping" sheetId="7" r:id="R349ebff5c3ea4387"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Payload_Response" sheetId="8" r:id="Rd2501ccd0801486d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Scale_Rules" sheetId="9" r:id="Rcefed3ae32624db7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Backlog" sheetId="10" r:id="R700867b192a14ed2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_API_Counts" sheetId="11" r:id="R79bb4850ac4b40fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cloudinary_Posts_QA_Update" sheetId="12" r:id="R0cb796506f2a4c46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Verification_2026-06-22" sheetId="13" r:id="R4618035700954e41"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -327,7 +327,7 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:cols>
     <x:col min="1" max="1" width="15.109999656677246" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="62.220001220703125" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="70.77999877929688" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="66.33000183105469" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.110000133514404" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="50.439998626708984" hidden="0" customWidth="1"/>
@@ -355,7 +355,7 @@
         <x:v>Backend structure</x:v>
       </x:c>
       <x:c r="B2" s="2" t="str">
-        <x:v>API catalog 168 routes ต่อ backend/components และฐานจริง</x:v>
+        <x:v>API catalog 169 routes ต่อ backend/components และฐานจริง</x:v>
       </x:c>
       <x:c r="C2" s="2" t="str">
         <x:v>คง HTTP layer บางและแยก repository/persistence ตาม feature</x:v>
@@ -406,10 +406,10 @@
         <x:v>Check-in</x:v>
       </x:c>
       <x:c r="B5" s="2" t="str">
-        <x:v>หน้า Check-in โหลด locations และ POST checkins จริง</x:v>
+        <x:v>หน้า Check-in โหลด locations และ POST checkins จริง พร้อม snapshot สถานที่จริงจาก GPS</x:v>
       </x:c>
       <x:c r="C5" s="2" t="str">
-        <x:v>ใช้ CPAC local location id และ GPS จริง</x:v>
+        <x:v>ใช้ CPAC local location id, GPS จริง และ actual_location_*_snapshot</x:v>
       </x:c>
       <x:c r="D5" s="2" t="str">
         <x:v>P0</x:v>
@@ -915,13 +915,13 @@
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="2" t="str">
-        <x:v>Notifications</x:v>
+        <x:v>Reports</x:v>
       </x:c>
       <x:c r="B9" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D9" s="2" t="n">
         <x:v>0</x:v>
@@ -932,7 +932,7 @@
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="2" t="str">
-        <x:v>Reports</x:v>
+        <x:v>Notifications</x:v>
       </x:c>
       <x:c r="B10" s="2" t="n">
         <x:v>7</x:v>
@@ -1224,16 +1224,16 @@
         <x:v>TOTAL</x:v>
       </x:c>
       <x:c r="B27" s="2" t="n">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C27" s="2" t="n">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D27" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E27" s="2" t="str">
-        <x:v>168 routes ใน registry/OpenAPI</x:v>
+        <x:v>169 routes ใน registry/OpenAPI</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1528,12 +1528,12 @@
     <x:col min="3" max="3" width="65.22000122070312" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="54.220001220703125" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="24.889999389648438" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="32.560001373291016" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="38.11000061035156" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="16.329999923706055" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="20.110000610351562" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="19" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="6.78000020980835" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="61" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="75.66999816894531" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -5636,55 +5636,57 @@
         <x:v>GET</x:v>
       </x:c>
       <x:c r="C119" s="2" t="str">
-        <x:v>/api/safety-effort/reports/findings?from=&amp;to=&amp;status=&amp;page=&amp;pageSize=</x:v>
+        <x:v>/api/safety-effort/reports/linewalk-overview?from=&amp;to=</x:v>
       </x:c>
       <x:c r="D119" s="2" t="str">
-        <x:v>รายงาน finding</x:v>
+        <x:v>ภาพรวม Line walk จาก submission จริง แยกพื้นที่ สถานะ และ BU</x:v>
       </x:c>
       <x:c r="E119" s="2" t="str">
         <x:v>Safety Admin</x:v>
       </x:c>
       <x:c r="F119" s="2" t="str">
-        <x:v>open report</x:v>
+        <x:v>เปิด dashboard ภาพรวมการประเมินความปลอดภัย</x:v>
       </x:c>
       <x:c r="G119" s="2" t="str">
         <x:v>Admin</x:v>
       </x:c>
       <x:c r="H119" s="2" t="str">
-        <x:v>Required</x:v>
+        <x:v>Aggregate</x:v>
       </x:c>
       <x:c r="I119" s="2" t="str">
-        <x:v>High</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="J119" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K119" s="2" t="str"/>
+      <x:c r="K119" s="2" t="str">
+        <x:v>อ่าน safety_effort_submissions.answers_json และ join checkins/locations/plant_location_details</x:v>
+      </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
       <x:c r="A120" s="2" t="str">
         <x:v>Reports</x:v>
       </x:c>
       <x:c r="B120" s="2" t="str">
-        <x:v>POST</x:v>
+        <x:v>GET</x:v>
       </x:c>
       <x:c r="C120" s="2" t="str">
-        <x:v>/api/exports</x:v>
+        <x:v>/api/safety-effort/reports/findings?from=&amp;to=&amp;status=&amp;page=&amp;pageSize=</x:v>
       </x:c>
       <x:c r="D120" s="2" t="str">
-        <x:v>สร้าง export job</x:v>
+        <x:v>รายงาน finding</x:v>
       </x:c>
       <x:c r="E120" s="2" t="str">
-        <x:v>Admin</x:v>
+        <x:v>Safety Admin</x:v>
       </x:c>
       <x:c r="F120" s="2" t="str">
-        <x:v>กด export ใหญ่</x:v>
+        <x:v>open report</x:v>
       </x:c>
       <x:c r="G120" s="2" t="str">
         <x:v>Admin</x:v>
       </x:c>
       <x:c r="H120" s="2" t="str">
-        <x:v>Async</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="I120" s="2" t="str">
         <x:v>High</x:v>
@@ -5692,42 +5694,42 @@
       <x:c r="J120" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K120" s="2" t="str">
-        <x:v>ใช้ได้หลาย module</x:v>
-      </x:c>
+      <x:c r="K120" s="2" t="str"/>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
       <x:c r="A121" s="2" t="str">
         <x:v>Reports</x:v>
       </x:c>
       <x:c r="B121" s="2" t="str">
-        <x:v>GET</x:v>
+        <x:v>POST</x:v>
       </x:c>
       <x:c r="C121" s="2" t="str">
-        <x:v>/api/exports/:id</x:v>
+        <x:v>/api/exports</x:v>
       </x:c>
       <x:c r="D121" s="2" t="str">
-        <x:v>สถานะ export job</x:v>
+        <x:v>สร้าง export job</x:v>
       </x:c>
       <x:c r="E121" s="2" t="str">
         <x:v>Admin</x:v>
       </x:c>
       <x:c r="F121" s="2" t="str">
-        <x:v>poll status</x:v>
+        <x:v>กด export ใหญ่</x:v>
       </x:c>
       <x:c r="G121" s="2" t="str">
         <x:v>Admin</x:v>
       </x:c>
       <x:c r="H121" s="2" t="str">
-        <x:v>No</x:v>
+        <x:v>Async</x:v>
       </x:c>
       <x:c r="I121" s="2" t="str">
-        <x:v>Small</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="J121" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K121" s="2" t="str"/>
+      <x:c r="K121" s="2" t="str">
+        <x:v>ใช้ได้หลาย module</x:v>
+      </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
       <x:c r="A122" s="2" t="str">
@@ -5737,65 +5739,65 @@
         <x:v>GET</x:v>
       </x:c>
       <x:c r="C122" s="2" t="str">
-        <x:v>/api/exports/:id/download</x:v>
+        <x:v>/api/exports/:id</x:v>
       </x:c>
       <x:c r="D122" s="2" t="str">
-        <x:v>download export file</x:v>
+        <x:v>สถานะ export job</x:v>
       </x:c>
       <x:c r="E122" s="2" t="str">
         <x:v>Admin</x:v>
       </x:c>
       <x:c r="F122" s="2" t="str">
-        <x:v>download</x:v>
+        <x:v>poll status</x:v>
       </x:c>
       <x:c r="G122" s="2" t="str">
         <x:v>Admin</x:v>
       </x:c>
       <x:c r="H122" s="2" t="str">
-        <x:v>File</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="I122" s="2" t="str">
-        <x:v>File</x:v>
+        <x:v>Small</x:v>
       </x:c>
       <x:c r="J122" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K122" s="2" t="str">
-        <x:v>signed URL or stream</x:v>
-      </x:c>
+      <x:c r="K122" s="2" t="str"/>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
       <x:c r="A123" s="2" t="str">
-        <x:v>Corrective Action</x:v>
+        <x:v>Reports</x:v>
       </x:c>
       <x:c r="B123" s="2" t="str">
         <x:v>GET</x:v>
       </x:c>
       <x:c r="C123" s="2" t="str">
-        <x:v>/api/safety-effort/findings?status=&amp;severity=&amp;page=&amp;pageSize=</x:v>
+        <x:v>/api/exports/:id/download</x:v>
       </x:c>
       <x:c r="D123" s="2" t="str">
-        <x:v>รายการ findings</x:v>
+        <x:v>download export file</x:v>
       </x:c>
       <x:c r="E123" s="2" t="str">
-        <x:v>Admin/Dashboard</x:v>
+        <x:v>Admin</x:v>
       </x:c>
       <x:c r="F123" s="2" t="str">
-        <x:v>ติดตามจุดเสี่ยง</x:v>
+        <x:v>download</x:v>
       </x:c>
       <x:c r="G123" s="2" t="str">
-        <x:v>User/Admin</x:v>
+        <x:v>Admin</x:v>
       </x:c>
       <x:c r="H123" s="2" t="str">
-        <x:v>Required</x:v>
+        <x:v>File</x:v>
       </x:c>
       <x:c r="I123" s="2" t="str">
-        <x:v>High</x:v>
+        <x:v>File</x:v>
       </x:c>
       <x:c r="J123" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K123" s="2" t="str"/>
+      <x:c r="K123" s="2" t="str">
+        <x:v>signed URL or stream</x:v>
+      </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
       <x:c r="A124" s="2" t="str">
@@ -5805,65 +5807,65 @@
         <x:v>GET</x:v>
       </x:c>
       <x:c r="C124" s="2" t="str">
-        <x:v>/api/safety-effort/findings/:id</x:v>
+        <x:v>/api/safety-effort/findings?status=&amp;severity=&amp;page=&amp;pageSize=</x:v>
       </x:c>
       <x:c r="D124" s="2" t="str">
-        <x:v>รายละเอียด finding</x:v>
+        <x:v>รายการ findings</x:v>
       </x:c>
       <x:c r="E124" s="2" t="str">
-        <x:v>Admin/Assignee</x:v>
+        <x:v>Admin/Dashboard</x:v>
       </x:c>
       <x:c r="F124" s="2" t="str">
-        <x:v>open detail</x:v>
+        <x:v>ติดตามจุดเสี่ยง</x:v>
       </x:c>
       <x:c r="G124" s="2" t="str">
         <x:v>User/Admin</x:v>
       </x:c>
       <x:c r="H124" s="2" t="str">
-        <x:v>No</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="I124" s="2" t="str">
-        <x:v>Medium</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="J124" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K124" s="2" t="str">
-        <x:v>รวม action/media</x:v>
-      </x:c>
+      <x:c r="K124" s="2" t="str"/>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
       <x:c r="A125" s="2" t="str">
         <x:v>Corrective Action</x:v>
       </x:c>
       <x:c r="B125" s="2" t="str">
-        <x:v>PATCH</x:v>
+        <x:v>GET</x:v>
       </x:c>
       <x:c r="C125" s="2" t="str">
         <x:v>/api/safety-effort/findings/:id</x:v>
       </x:c>
       <x:c r="D125" s="2" t="str">
-        <x:v>แก้ finding</x:v>
+        <x:v>รายละเอียด finding</x:v>
       </x:c>
       <x:c r="E125" s="2" t="str">
-        <x:v>Admin/Reporter</x:v>
+        <x:v>Admin/Assignee</x:v>
       </x:c>
       <x:c r="F125" s="2" t="str">
-        <x:v>save</x:v>
+        <x:v>open detail</x:v>
       </x:c>
       <x:c r="G125" s="2" t="str">
-        <x:v>Owner/Admin</x:v>
+        <x:v>User/Admin</x:v>
       </x:c>
       <x:c r="H125" s="2" t="str">
         <x:v>No</x:v>
       </x:c>
       <x:c r="I125" s="2" t="str">
-        <x:v>Small</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="J125" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K125" s="2" t="str"/>
+      <x:c r="K125" s="2" t="str">
+        <x:v>รวม action/media</x:v>
+      </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
       <x:c r="A126" s="2" t="str">
@@ -5873,19 +5875,19 @@
         <x:v>PATCH</x:v>
       </x:c>
       <x:c r="C126" s="2" t="str">
-        <x:v>/api/safety-effort/corrective-actions/:id</x:v>
+        <x:v>/api/safety-effort/findings/:id</x:v>
       </x:c>
       <x:c r="D126" s="2" t="str">
-        <x:v>อัปเดต action</x:v>
+        <x:v>แก้ finding</x:v>
       </x:c>
       <x:c r="E126" s="2" t="str">
-        <x:v>Assignee/Admin</x:v>
+        <x:v>Admin/Reporter</x:v>
       </x:c>
       <x:c r="F126" s="2" t="str">
-        <x:v>update status</x:v>
+        <x:v>save</x:v>
       </x:c>
       <x:c r="G126" s="2" t="str">
-        <x:v>Assignee/Admin</x:v>
+        <x:v>Owner/Admin</x:v>
       </x:c>
       <x:c r="H126" s="2" t="str">
         <x:v>No</x:v>
@@ -5903,19 +5905,19 @@
         <x:v>Corrective Action</x:v>
       </x:c>
       <x:c r="B127" s="2" t="str">
-        <x:v>POST</x:v>
+        <x:v>PATCH</x:v>
       </x:c>
       <x:c r="C127" s="2" t="str">
-        <x:v>/api/safety-effort/corrective-actions/:id/complete</x:v>
+        <x:v>/api/safety-effort/corrective-actions/:id</x:v>
       </x:c>
       <x:c r="D127" s="2" t="str">
-        <x:v>ปิดงานแก้ไข</x:v>
+        <x:v>อัปเดต action</x:v>
       </x:c>
       <x:c r="E127" s="2" t="str">
         <x:v>Assignee/Admin</x:v>
       </x:c>
       <x:c r="F127" s="2" t="str">
-        <x:v>complete</x:v>
+        <x:v>update status</x:v>
       </x:c>
       <x:c r="G127" s="2" t="str">
         <x:v>Assignee/Admin</x:v>
@@ -5929,9 +5931,7 @@
       <x:c r="J127" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K127" s="2" t="str">
-        <x:v>require evidence optional</x:v>
-      </x:c>
+      <x:c r="K127" s="2" t="str"/>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
       <x:c r="A128" s="2" t="str">
@@ -5941,19 +5941,19 @@
         <x:v>POST</x:v>
       </x:c>
       <x:c r="C128" s="2" t="str">
-        <x:v>/api/safety-effort/corrective-actions/:id/comments</x:v>
+        <x:v>/api/safety-effort/corrective-actions/:id/complete</x:v>
       </x:c>
       <x:c r="D128" s="2" t="str">
-        <x:v>comment ใน action</x:v>
+        <x:v>ปิดงานแก้ไข</x:v>
       </x:c>
       <x:c r="E128" s="2" t="str">
         <x:v>Assignee/Admin</x:v>
       </x:c>
       <x:c r="F128" s="2" t="str">
-        <x:v>add comment</x:v>
+        <x:v>complete</x:v>
       </x:c>
       <x:c r="G128" s="2" t="str">
-        <x:v>User</x:v>
+        <x:v>Assignee/Admin</x:v>
       </x:c>
       <x:c r="H128" s="2" t="str">
         <x:v>No</x:v>
@@ -5964,35 +5964,37 @@
       <x:c r="J128" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K128" s="2" t="str"/>
+      <x:c r="K128" s="2" t="str">
+        <x:v>require evidence optional</x:v>
+      </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
       <x:c r="A129" s="2" t="str">
-        <x:v>Safety Culture Admin</x:v>
+        <x:v>Corrective Action</x:v>
       </x:c>
       <x:c r="B129" s="2" t="str">
-        <x:v>GET</x:v>
+        <x:v>POST</x:v>
       </x:c>
       <x:c r="C129" s="2" t="str">
-        <x:v>/api/safety-culture/posts/admin?status=&amp;page=&amp;pageSize=</x:v>
+        <x:v>/api/safety-effort/corrective-actions/:id/comments</x:v>
       </x:c>
       <x:c r="D129" s="2" t="str">
-        <x:v>admin moderation list</x:v>
+        <x:v>comment ใน action</x:v>
       </x:c>
       <x:c r="E129" s="2" t="str">
-        <x:v>Admin Culture</x:v>
+        <x:v>Assignee/Admin</x:v>
       </x:c>
       <x:c r="F129" s="2" t="str">
-        <x:v>เปิดจัดการโพสต์</x:v>
+        <x:v>add comment</x:v>
       </x:c>
       <x:c r="G129" s="2" t="str">
-        <x:v>Admin</x:v>
+        <x:v>User</x:v>
       </x:c>
       <x:c r="H129" s="2" t="str">
-        <x:v>Required</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="I129" s="2" t="str">
-        <x:v>High</x:v>
+        <x:v>Small</x:v>
       </x:c>
       <x:c r="J129" s="2" t="str">
         <x:v>Existing</x:v>
@@ -6004,35 +6006,33 @@
         <x:v>Safety Culture Admin</x:v>
       </x:c>
       <x:c r="B130" s="2" t="str">
-        <x:v>POST</x:v>
+        <x:v>GET</x:v>
       </x:c>
       <x:c r="C130" s="2" t="str">
-        <x:v>/api/safety-culture/posts/:id/approve</x:v>
+        <x:v>/api/safety-culture/posts/admin?status=&amp;page=&amp;pageSize=</x:v>
       </x:c>
       <x:c r="D130" s="2" t="str">
-        <x:v>approve post</x:v>
+        <x:v>admin moderation list</x:v>
       </x:c>
       <x:c r="E130" s="2" t="str">
         <x:v>Admin Culture</x:v>
       </x:c>
       <x:c r="F130" s="2" t="str">
-        <x:v>approve</x:v>
+        <x:v>เปิดจัดการโพสต์</x:v>
       </x:c>
       <x:c r="G130" s="2" t="str">
         <x:v>Admin</x:v>
       </x:c>
       <x:c r="H130" s="2" t="str">
-        <x:v>No</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="I130" s="2" t="str">
-        <x:v>Small</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="J130" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K130" s="2" t="str">
-        <x:v>optional if moderation enabled</x:v>
-      </x:c>
+      <x:c r="K130" s="2" t="str"/>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
       <x:c r="A131" s="2" t="str">
@@ -6042,16 +6042,16 @@
         <x:v>POST</x:v>
       </x:c>
       <x:c r="C131" s="2" t="str">
-        <x:v>/api/safety-culture/posts/:id/reject</x:v>
+        <x:v>/api/safety-culture/posts/:id/approve</x:v>
       </x:c>
       <x:c r="D131" s="2" t="str">
-        <x:v>reject post</x:v>
+        <x:v>approve post</x:v>
       </x:c>
       <x:c r="E131" s="2" t="str">
         <x:v>Admin Culture</x:v>
       </x:c>
       <x:c r="F131" s="2" t="str">
-        <x:v>reject</x:v>
+        <x:v>approve</x:v>
       </x:c>
       <x:c r="G131" s="2" t="str">
         <x:v>Admin</x:v>
@@ -6066,66 +6066,68 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K131" s="2" t="str">
-        <x:v>with reason</x:v>
+        <x:v>optional if moderation enabled</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
       <x:c r="A132" s="2" t="str">
-        <x:v>Safety Culture</x:v>
+        <x:v>Safety Culture Admin</x:v>
       </x:c>
       <x:c r="B132" s="2" t="str">
-        <x:v>GET</x:v>
+        <x:v>POST</x:v>
       </x:c>
       <x:c r="C132" s="2" t="str">
-        <x:v>/api/safety-culture/events/:id</x:v>
+        <x:v>/api/safety-culture/posts/:id/reject</x:v>
       </x:c>
       <x:c r="D132" s="2" t="str">
-        <x:v>รายละเอียดกิจกรรม</x:v>
+        <x:v>reject post</x:v>
       </x:c>
       <x:c r="E132" s="2" t="str">
-        <x:v>Feed/Admin</x:v>
+        <x:v>Admin Culture</x:v>
       </x:c>
       <x:c r="F132" s="2" t="str">
-        <x:v>open event</x:v>
+        <x:v>reject</x:v>
       </x:c>
       <x:c r="G132" s="2" t="str">
-        <x:v>User</x:v>
+        <x:v>Admin</x:v>
       </x:c>
       <x:c r="H132" s="2" t="str">
         <x:v>No</x:v>
       </x:c>
       <x:c r="I132" s="2" t="str">
-        <x:v>Medium</x:v>
+        <x:v>Small</x:v>
       </x:c>
       <x:c r="J132" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K132" s="2" t="str"/>
+      <x:c r="K132" s="2" t="str">
+        <x:v>with reason</x:v>
+      </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
       <x:c r="A133" s="2" t="str">
         <x:v>Safety Culture</x:v>
       </x:c>
       <x:c r="B133" s="2" t="str">
-        <x:v>POST</x:v>
+        <x:v>GET</x:v>
       </x:c>
       <x:c r="C133" s="2" t="str">
-        <x:v>/api/safety-culture/events/:id/notify</x:v>
+        <x:v>/api/safety-culture/events/:id</x:v>
       </x:c>
       <x:c r="D133" s="2" t="str">
-        <x:v>ส่ง notification กิจกรรม</x:v>
+        <x:v>รายละเอียดกิจกรรม</x:v>
       </x:c>
       <x:c r="E133" s="2" t="str">
-        <x:v>Admin Event</x:v>
+        <x:v>Feed/Admin</x:v>
       </x:c>
       <x:c r="F133" s="2" t="str">
-        <x:v>กดส่งแจ้งเตือน</x:v>
+        <x:v>open event</x:v>
       </x:c>
       <x:c r="G133" s="2" t="str">
-        <x:v>Admin</x:v>
+        <x:v>User</x:v>
       </x:c>
       <x:c r="H133" s="2" t="str">
-        <x:v>Batch/queue</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="I133" s="2" t="str">
         <x:v>Medium</x:v>
@@ -6140,28 +6142,28 @@
         <x:v>Safety Culture</x:v>
       </x:c>
       <x:c r="B134" s="2" t="str">
-        <x:v>GET</x:v>
+        <x:v>POST</x:v>
       </x:c>
       <x:c r="C134" s="2" t="str">
-        <x:v>/api/safety-culture/points/me</x:v>
+        <x:v>/api/safety-culture/events/:id/notify</x:v>
       </x:c>
       <x:c r="D134" s="2" t="str">
-        <x:v>คะแนนของฉัน</x:v>
+        <x:v>ส่ง notification กิจกรรม</x:v>
       </x:c>
       <x:c r="E134" s="2" t="str">
-        <x:v>Profile/Rewards</x:v>
+        <x:v>Admin Event</x:v>
       </x:c>
       <x:c r="F134" s="2" t="str">
-        <x:v>เปิดหน้า</x:v>
+        <x:v>กดส่งแจ้งเตือน</x:v>
       </x:c>
       <x:c r="G134" s="2" t="str">
-        <x:v>User</x:v>
+        <x:v>Admin</x:v>
       </x:c>
       <x:c r="H134" s="2" t="str">
-        <x:v>No</x:v>
+        <x:v>Batch/queue</x:v>
       </x:c>
       <x:c r="I134" s="2" t="str">
-        <x:v>Small</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="J134" s="2" t="str">
         <x:v>Existing</x:v>
@@ -6176,25 +6178,25 @@
         <x:v>GET</x:v>
       </x:c>
       <x:c r="C135" s="2" t="str">
-        <x:v>/api/safety-culture/points/me/transactions?cursor=&amp;limit=</x:v>
+        <x:v>/api/safety-culture/points/me</x:v>
       </x:c>
       <x:c r="D135" s="2" t="str">
-        <x:v>ledger คะแนนของฉัน</x:v>
+        <x:v>คะแนนของฉัน</x:v>
       </x:c>
       <x:c r="E135" s="2" t="str">
-        <x:v>Profile history</x:v>
+        <x:v>Profile/Rewards</x:v>
       </x:c>
       <x:c r="F135" s="2" t="str">
-        <x:v>scroll</x:v>
+        <x:v>เปิดหน้า</x:v>
       </x:c>
       <x:c r="G135" s="2" t="str">
         <x:v>User</x:v>
       </x:c>
       <x:c r="H135" s="2" t="str">
-        <x:v>Cursor</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="I135" s="2" t="str">
-        <x:v>Medium</x:v>
+        <x:v>Small</x:v>
       </x:c>
       <x:c r="J135" s="2" t="str">
         <x:v>Existing</x:v>
@@ -6203,31 +6205,31 @@
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
       <x:c r="A136" s="2" t="str">
-        <x:v>Safety Culture Admin</x:v>
+        <x:v>Safety Culture</x:v>
       </x:c>
       <x:c r="B136" s="2" t="str">
         <x:v>GET</x:v>
       </x:c>
       <x:c r="C136" s="2" t="str">
-        <x:v>/api/safety-culture/points/rules</x:v>
+        <x:v>/api/safety-culture/points/me/transactions?cursor=&amp;limit=</x:v>
       </x:c>
       <x:c r="D136" s="2" t="str">
-        <x:v>กติกาคะแนน</x:v>
+        <x:v>ledger คะแนนของฉัน</x:v>
       </x:c>
       <x:c r="E136" s="2" t="str">
-        <x:v>Admin</x:v>
+        <x:v>Profile history</x:v>
       </x:c>
       <x:c r="F136" s="2" t="str">
-        <x:v>open settings</x:v>
+        <x:v>scroll</x:v>
       </x:c>
       <x:c r="G136" s="2" t="str">
-        <x:v>Admin</x:v>
+        <x:v>User</x:v>
       </x:c>
       <x:c r="H136" s="2" t="str">
-        <x:v>No</x:v>
+        <x:v>Cursor</x:v>
       </x:c>
       <x:c r="I136" s="2" t="str">
-        <x:v>Small</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="J136" s="2" t="str">
         <x:v>Existing</x:v>
@@ -6239,19 +6241,19 @@
         <x:v>Safety Culture Admin</x:v>
       </x:c>
       <x:c r="B137" s="2" t="str">
-        <x:v>PATCH</x:v>
+        <x:v>GET</x:v>
       </x:c>
       <x:c r="C137" s="2" t="str">
-        <x:v>/api/safety-culture/points/rules/:id</x:v>
+        <x:v>/api/safety-culture/points/rules</x:v>
       </x:c>
       <x:c r="D137" s="2" t="str">
-        <x:v>แก้กติกาคะแนน</x:v>
+        <x:v>กติกาคะแนน</x:v>
       </x:c>
       <x:c r="E137" s="2" t="str">
         <x:v>Admin</x:v>
       </x:c>
       <x:c r="F137" s="2" t="str">
-        <x:v>save rule</x:v>
+        <x:v>open settings</x:v>
       </x:c>
       <x:c r="G137" s="2" t="str">
         <x:v>Admin</x:v>
@@ -6265,28 +6267,26 @@
       <x:c r="J137" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K137" s="2" t="str">
-        <x:v>audit required</x:v>
-      </x:c>
+      <x:c r="K137" s="2" t="str"/>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
       <x:c r="A138" s="2" t="str">
         <x:v>Safety Culture Admin</x:v>
       </x:c>
       <x:c r="B138" s="2" t="str">
-        <x:v>POST</x:v>
+        <x:v>PATCH</x:v>
       </x:c>
       <x:c r="C138" s="2" t="str">
-        <x:v>/api/safety-culture/points/adjustments</x:v>
+        <x:v>/api/safety-culture/points/rules/:id</x:v>
       </x:c>
       <x:c r="D138" s="2" t="str">
-        <x:v>ปรับคะแนน manual</x:v>
+        <x:v>แก้กติกาคะแนน</x:v>
       </x:c>
       <x:c r="E138" s="2" t="str">
         <x:v>Admin</x:v>
       </x:c>
       <x:c r="F138" s="2" t="str">
-        <x:v>manual adjustment</x:v>
+        <x:v>save rule</x:v>
       </x:c>
       <x:c r="G138" s="2" t="str">
         <x:v>Admin</x:v>
@@ -6301,27 +6301,27 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K138" s="2" t="str">
-        <x:v>audit + reason required</x:v>
+        <x:v>audit required</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="15" hidden="0" customHeight="1">
       <x:c r="A139" s="2" t="str">
-        <x:v>Rewards Admin</x:v>
+        <x:v>Safety Culture Admin</x:v>
       </x:c>
       <x:c r="B139" s="2" t="str">
         <x:v>POST</x:v>
       </x:c>
       <x:c r="C139" s="2" t="str">
-        <x:v>/api/safety-culture/rewards</x:v>
+        <x:v>/api/safety-culture/points/adjustments</x:v>
       </x:c>
       <x:c r="D139" s="2" t="str">
-        <x:v>สร้างของรางวัล</x:v>
+        <x:v>ปรับคะแนน manual</x:v>
       </x:c>
       <x:c r="E139" s="2" t="str">
-        <x:v>Admin Reward</x:v>
+        <x:v>Admin</x:v>
       </x:c>
       <x:c r="F139" s="2" t="str">
-        <x:v>save</x:v>
+        <x:v>manual adjustment</x:v>
       </x:c>
       <x:c r="G139" s="2" t="str">
         <x:v>Admin</x:v>
@@ -6336,7 +6336,7 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K139" s="2" t="str">
-        <x:v>reward image mediaId</x:v>
+        <x:v>audit + reason required</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -6344,13 +6344,13 @@
         <x:v>Rewards Admin</x:v>
       </x:c>
       <x:c r="B140" s="2" t="str">
-        <x:v>PATCH</x:v>
+        <x:v>POST</x:v>
       </x:c>
       <x:c r="C140" s="2" t="str">
-        <x:v>/api/safety-culture/rewards/:id</x:v>
+        <x:v>/api/safety-culture/rewards</x:v>
       </x:c>
       <x:c r="D140" s="2" t="str">
-        <x:v>แก้ของรางวัล</x:v>
+        <x:v>สร้างของรางวัล</x:v>
       </x:c>
       <x:c r="E140" s="2" t="str">
         <x:v>Admin Reward</x:v>
@@ -6370,26 +6370,28 @@
       <x:c r="J140" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K140" s="2" t="str"/>
+      <x:c r="K140" s="2" t="str">
+        <x:v>reward image mediaId</x:v>
+      </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
       <x:c r="A141" s="2" t="str">
         <x:v>Rewards Admin</x:v>
       </x:c>
       <x:c r="B141" s="2" t="str">
-        <x:v>DELETE</x:v>
+        <x:v>PATCH</x:v>
       </x:c>
       <x:c r="C141" s="2" t="str">
         <x:v>/api/safety-culture/rewards/:id</x:v>
       </x:c>
       <x:c r="D141" s="2" t="str">
-        <x:v>ซ่อน/ลบของรางวัล</x:v>
+        <x:v>แก้ของรางวัล</x:v>
       </x:c>
       <x:c r="E141" s="2" t="str">
         <x:v>Admin Reward</x:v>
       </x:c>
       <x:c r="F141" s="2" t="str">
-        <x:v>delete</x:v>
+        <x:v>save</x:v>
       </x:c>
       <x:c r="G141" s="2" t="str">
         <x:v>Admin</x:v>
@@ -6403,96 +6405,94 @@
       <x:c r="J141" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K141" s="2" t="str">
-        <x:v>soft delete</x:v>
-      </x:c>
+      <x:c r="K141" s="2" t="str"/>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
       <x:c r="A142" s="2" t="str">
         <x:v>Rewards Admin</x:v>
       </x:c>
       <x:c r="B142" s="2" t="str">
-        <x:v>GET</x:v>
+        <x:v>DELETE</x:v>
       </x:c>
       <x:c r="C142" s="2" t="str">
-        <x:v>/api/safety-culture/reward-redemptions?status=&amp;page=&amp;pageSize=</x:v>
+        <x:v>/api/safety-culture/rewards/:id</x:v>
       </x:c>
       <x:c r="D142" s="2" t="str">
-        <x:v>รายการแลกรางวัล</x:v>
+        <x:v>ซ่อน/ลบของรางวัล</x:v>
       </x:c>
       <x:c r="E142" s="2" t="str">
         <x:v>Admin Reward</x:v>
       </x:c>
       <x:c r="F142" s="2" t="str">
-        <x:v>เปิด admin</x:v>
+        <x:v>delete</x:v>
       </x:c>
       <x:c r="G142" s="2" t="str">
         <x:v>Admin</x:v>
       </x:c>
       <x:c r="H142" s="2" t="str">
-        <x:v>Required</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="I142" s="2" t="str">
-        <x:v>High</x:v>
+        <x:v>Small</x:v>
       </x:c>
       <x:c r="J142" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K142" s="2" t="str"/>
+      <x:c r="K142" s="2" t="str">
+        <x:v>soft delete</x:v>
+      </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
       <x:c r="A143" s="2" t="str">
         <x:v>Rewards Admin</x:v>
       </x:c>
       <x:c r="B143" s="2" t="str">
-        <x:v>PATCH</x:v>
+        <x:v>GET</x:v>
       </x:c>
       <x:c r="C143" s="2" t="str">
-        <x:v>/api/safety-culture/reward-redemptions/:id/status</x:v>
+        <x:v>/api/safety-culture/reward-redemptions?status=&amp;page=&amp;pageSize=</x:v>
       </x:c>
       <x:c r="D143" s="2" t="str">
-        <x:v>อัปเดตสถานะแลกรางวัล</x:v>
+        <x:v>รายการแลกรางวัล</x:v>
       </x:c>
       <x:c r="E143" s="2" t="str">
         <x:v>Admin Reward</x:v>
       </x:c>
       <x:c r="F143" s="2" t="str">
-        <x:v>approve/fulfill/cancel</x:v>
+        <x:v>เปิด admin</x:v>
       </x:c>
       <x:c r="G143" s="2" t="str">
         <x:v>Admin</x:v>
       </x:c>
       <x:c r="H143" s="2" t="str">
-        <x:v>No</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="I143" s="2" t="str">
-        <x:v>Small</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="J143" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K143" s="2" t="str">
-        <x:v>transaction-safe</x:v>
-      </x:c>
+      <x:c r="K143" s="2" t="str"/>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
       <x:c r="A144" s="2" t="str">
         <x:v>Rewards Admin</x:v>
       </x:c>
       <x:c r="B144" s="2" t="str">
-        <x:v>POST</x:v>
+        <x:v>PATCH</x:v>
       </x:c>
       <x:c r="C144" s="2" t="str">
-        <x:v>/api/safety-culture/rewards/:id/inventory-transactions</x:v>
+        <x:v>/api/safety-culture/reward-redemptions/:id/status</x:v>
       </x:c>
       <x:c r="D144" s="2" t="str">
-        <x:v>ปรับ stock ของรางวัล</x:v>
+        <x:v>อัปเดตสถานะแลกรางวัล</x:v>
       </x:c>
       <x:c r="E144" s="2" t="str">
         <x:v>Admin Reward</x:v>
       </x:c>
       <x:c r="F144" s="2" t="str">
-        <x:v>stock in/out</x:v>
+        <x:v>approve/fulfill/cancel</x:v>
       </x:c>
       <x:c r="G144" s="2" t="str">
         <x:v>Admin</x:v>
@@ -6507,69 +6507,71 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K144" s="2" t="str">
-        <x:v>ledger</x:v>
+        <x:v>transaction-safe</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="15" hidden="0" customHeight="1">
       <x:c r="A145" s="2" t="str">
-        <x:v>Awareness Admin</x:v>
+        <x:v>Rewards Admin</x:v>
       </x:c>
       <x:c r="B145" s="2" t="str">
-        <x:v>GET</x:v>
+        <x:v>POST</x:v>
       </x:c>
       <x:c r="C145" s="2" t="str">
-        <x:v>/api/safety-awareness/questions/admin?page=&amp;pageSize=&amp;category=</x:v>
+        <x:v>/api/safety-culture/rewards/:id/inventory-transactions</x:v>
       </x:c>
       <x:c r="D145" s="2" t="str">
-        <x:v>คลังคำถาม awareness</x:v>
+        <x:v>ปรับ stock ของรางวัล</x:v>
       </x:c>
       <x:c r="E145" s="2" t="str">
-        <x:v>Admin Awareness</x:v>
+        <x:v>Admin Reward</x:v>
       </x:c>
       <x:c r="F145" s="2" t="str">
-        <x:v>open admin</x:v>
+        <x:v>stock in/out</x:v>
       </x:c>
       <x:c r="G145" s="2" t="str">
         <x:v>Admin</x:v>
       </x:c>
       <x:c r="H145" s="2" t="str">
-        <x:v>Required</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="I145" s="2" t="str">
-        <x:v>Medium</x:v>
+        <x:v>Small</x:v>
       </x:c>
       <x:c r="J145" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K145" s="2" t="str"/>
+      <x:c r="K145" s="2" t="str">
+        <x:v>ledger</x:v>
+      </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
       <x:c r="A146" s="2" t="str">
         <x:v>Awareness Admin</x:v>
       </x:c>
       <x:c r="B146" s="2" t="str">
-        <x:v>POST</x:v>
+        <x:v>GET</x:v>
       </x:c>
       <x:c r="C146" s="2" t="str">
-        <x:v>/api/safety-awareness/questions</x:v>
+        <x:v>/api/safety-awareness/questions/admin?page=&amp;pageSize=&amp;category=</x:v>
       </x:c>
       <x:c r="D146" s="2" t="str">
-        <x:v>สร้างคำถาม awareness</x:v>
+        <x:v>คลังคำถาม awareness</x:v>
       </x:c>
       <x:c r="E146" s="2" t="str">
         <x:v>Admin Awareness</x:v>
       </x:c>
       <x:c r="F146" s="2" t="str">
-        <x:v>save</x:v>
+        <x:v>open admin</x:v>
       </x:c>
       <x:c r="G146" s="2" t="str">
         <x:v>Admin</x:v>
       </x:c>
       <x:c r="H146" s="2" t="str">
-        <x:v>No</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="I146" s="2" t="str">
-        <x:v>Small</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="J146" s="2" t="str">
         <x:v>Existing</x:v>
@@ -6581,13 +6583,13 @@
         <x:v>Awareness Admin</x:v>
       </x:c>
       <x:c r="B147" s="2" t="str">
-        <x:v>PATCH</x:v>
+        <x:v>POST</x:v>
       </x:c>
       <x:c r="C147" s="2" t="str">
-        <x:v>/api/safety-awareness/questions/:id</x:v>
+        <x:v>/api/safety-awareness/questions</x:v>
       </x:c>
       <x:c r="D147" s="2" t="str">
-        <x:v>แก้คำถาม awareness</x:v>
+        <x:v>สร้างคำถาม awareness</x:v>
       </x:c>
       <x:c r="E147" s="2" t="str">
         <x:v>Admin Awareness</x:v>
@@ -6614,19 +6616,19 @@
         <x:v>Awareness Admin</x:v>
       </x:c>
       <x:c r="B148" s="2" t="str">
-        <x:v>DELETE</x:v>
+        <x:v>PATCH</x:v>
       </x:c>
       <x:c r="C148" s="2" t="str">
         <x:v>/api/safety-awareness/questions/:id</x:v>
       </x:c>
       <x:c r="D148" s="2" t="str">
-        <x:v>disable คำถาม awareness</x:v>
+        <x:v>แก้คำถาม awareness</x:v>
       </x:c>
       <x:c r="E148" s="2" t="str">
         <x:v>Admin Awareness</x:v>
       </x:c>
       <x:c r="F148" s="2" t="str">
-        <x:v>delete</x:v>
+        <x:v>save</x:v>
       </x:c>
       <x:c r="G148" s="2" t="str">
         <x:v>Admin</x:v>
@@ -6640,70 +6642,70 @@
       <x:c r="J148" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K148" s="2" t="str">
-        <x:v>soft disable</x:v>
-      </x:c>
+      <x:c r="K148" s="2" t="str"/>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
       <x:c r="A149" s="2" t="str">
-        <x:v>Awareness</x:v>
+        <x:v>Awareness Admin</x:v>
       </x:c>
       <x:c r="B149" s="2" t="str">
-        <x:v>GET</x:v>
+        <x:v>DELETE</x:v>
       </x:c>
       <x:c r="C149" s="2" t="str">
-        <x:v>/api/safety-awareness/attempts/me?from=&amp;to=&amp;page=&amp;pageSize=</x:v>
+        <x:v>/api/safety-awareness/questions/:id</x:v>
       </x:c>
       <x:c r="D149" s="2" t="str">
-        <x:v>ประวัติ awareness ของฉัน</x:v>
+        <x:v>disable คำถาม awareness</x:v>
       </x:c>
       <x:c r="E149" s="2" t="str">
-        <x:v>Profile</x:v>
+        <x:v>Admin Awareness</x:v>
       </x:c>
       <x:c r="F149" s="2" t="str">
-        <x:v>open history</x:v>
+        <x:v>delete</x:v>
       </x:c>
       <x:c r="G149" s="2" t="str">
-        <x:v>User</x:v>
+        <x:v>Admin</x:v>
       </x:c>
       <x:c r="H149" s="2" t="str">
-        <x:v>Required</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="I149" s="2" t="str">
-        <x:v>Medium</x:v>
+        <x:v>Small</x:v>
       </x:c>
       <x:c r="J149" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K149" s="2" t="str"/>
+      <x:c r="K149" s="2" t="str">
+        <x:v>soft disable</x:v>
+      </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
       <x:c r="A150" s="2" t="str">
-        <x:v>Awareness Admin</x:v>
+        <x:v>Awareness</x:v>
       </x:c>
       <x:c r="B150" s="2" t="str">
         <x:v>GET</x:v>
       </x:c>
       <x:c r="C150" s="2" t="str">
-        <x:v>/api/safety-awareness/attempts?from=&amp;to=&amp;userId=&amp;page=&amp;pageSize=</x:v>
+        <x:v>/api/safety-awareness/attempts/me?from=&amp;to=&amp;page=&amp;pageSize=</x:v>
       </x:c>
       <x:c r="D150" s="2" t="str">
-        <x:v>รายงาน awareness</x:v>
+        <x:v>ประวัติ awareness ของฉัน</x:v>
       </x:c>
       <x:c r="E150" s="2" t="str">
-        <x:v>Admin Awareness</x:v>
+        <x:v>Profile</x:v>
       </x:c>
       <x:c r="F150" s="2" t="str">
-        <x:v>open report</x:v>
+        <x:v>open history</x:v>
       </x:c>
       <x:c r="G150" s="2" t="str">
-        <x:v>Admin</x:v>
+        <x:v>User</x:v>
       </x:c>
       <x:c r="H150" s="2" t="str">
         <x:v>Required</x:v>
       </x:c>
       <x:c r="I150" s="2" t="str">
-        <x:v>High</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="J150" s="2" t="str">
         <x:v>Existing</x:v>
@@ -6712,60 +6714,58 @@
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
       <x:c r="A151" s="2" t="str">
-        <x:v>Holidays</x:v>
+        <x:v>Awareness Admin</x:v>
       </x:c>
       <x:c r="B151" s="2" t="str">
         <x:v>GET</x:v>
       </x:c>
       <x:c r="C151" s="2" t="str">
-        <x:v>/api/holidays?year=</x:v>
+        <x:v>/api/safety-awareness/attempts?from=&amp;to=&amp;userId=&amp;page=&amp;pageSize=</x:v>
       </x:c>
       <x:c r="D151" s="2" t="str">
-        <x:v>รายการวันหยุด</x:v>
+        <x:v>รายงาน awareness</x:v>
       </x:c>
       <x:c r="E151" s="2" t="str">
-        <x:v>Admin Awareness/Effort</x:v>
+        <x:v>Admin Awareness</x:v>
       </x:c>
       <x:c r="F151" s="2" t="str">
-        <x:v>เปิด settings/date rules</x:v>
+        <x:v>open report</x:v>
       </x:c>
       <x:c r="G151" s="2" t="str">
-        <x:v>User/Admin</x:v>
+        <x:v>Admin</x:v>
       </x:c>
       <x:c r="H151" s="2" t="str">
-        <x:v>No</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="I151" s="2" t="str">
-        <x:v>Small</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="J151" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K151" s="2" t="str">
-        <x:v>cache yearly</x:v>
-      </x:c>
+      <x:c r="K151" s="2" t="str"/>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
       <x:c r="A152" s="2" t="str">
         <x:v>Holidays</x:v>
       </x:c>
       <x:c r="B152" s="2" t="str">
-        <x:v>POST</x:v>
+        <x:v>GET</x:v>
       </x:c>
       <x:c r="C152" s="2" t="str">
-        <x:v>/api/holidays</x:v>
+        <x:v>/api/holidays?year=</x:v>
       </x:c>
       <x:c r="D152" s="2" t="str">
-        <x:v>เพิ่มวันหยุด</x:v>
+        <x:v>รายการวันหยุด</x:v>
       </x:c>
       <x:c r="E152" s="2" t="str">
-        <x:v>Admin</x:v>
+        <x:v>Admin Awareness/Effort</x:v>
       </x:c>
       <x:c r="F152" s="2" t="str">
-        <x:v>save</x:v>
+        <x:v>เปิด settings/date rules</x:v>
       </x:c>
       <x:c r="G152" s="2" t="str">
-        <x:v>Admin</x:v>
+        <x:v>User/Admin</x:v>
       </x:c>
       <x:c r="H152" s="2" t="str">
         <x:v>No</x:v>
@@ -6776,26 +6776,28 @@
       <x:c r="J152" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K152" s="2" t="str"/>
+      <x:c r="K152" s="2" t="str">
+        <x:v>cache yearly</x:v>
+      </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
       <x:c r="A153" s="2" t="str">
         <x:v>Holidays</x:v>
       </x:c>
       <x:c r="B153" s="2" t="str">
-        <x:v>DELETE</x:v>
+        <x:v>POST</x:v>
       </x:c>
       <x:c r="C153" s="2" t="str">
-        <x:v>/api/holidays/:id</x:v>
+        <x:v>/api/holidays</x:v>
       </x:c>
       <x:c r="D153" s="2" t="str">
-        <x:v>ลบวันหยุด</x:v>
+        <x:v>เพิ่มวันหยุด</x:v>
       </x:c>
       <x:c r="E153" s="2" t="str">
         <x:v>Admin</x:v>
       </x:c>
       <x:c r="F153" s="2" t="str">
-        <x:v>delete</x:v>
+        <x:v>save</x:v>
       </x:c>
       <x:c r="G153" s="2" t="str">
         <x:v>Admin</x:v>
@@ -6813,25 +6815,25 @@
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
       <x:c r="A154" s="2" t="str">
-        <x:v>Notifications</x:v>
+        <x:v>Holidays</x:v>
       </x:c>
       <x:c r="B154" s="2" t="str">
-        <x:v>POST</x:v>
+        <x:v>DELETE</x:v>
       </x:c>
       <x:c r="C154" s="2" t="str">
-        <x:v>/api/notifications/:id/archive</x:v>
+        <x:v>/api/holidays/:id</x:v>
       </x:c>
       <x:c r="D154" s="2" t="str">
-        <x:v>archive notification</x:v>
+        <x:v>ลบวันหยุด</x:v>
       </x:c>
       <x:c r="E154" s="2" t="str">
-        <x:v>Notifications</x:v>
+        <x:v>Admin</x:v>
       </x:c>
       <x:c r="F154" s="2" t="str">
-        <x:v>archive</x:v>
+        <x:v>delete</x:v>
       </x:c>
       <x:c r="G154" s="2" t="str">
-        <x:v>User</x:v>
+        <x:v>Admin</x:v>
       </x:c>
       <x:c r="H154" s="2" t="str">
         <x:v>No</x:v>
@@ -6849,19 +6851,19 @@
         <x:v>Notifications</x:v>
       </x:c>
       <x:c r="B155" s="2" t="str">
-        <x:v>PATCH</x:v>
+        <x:v>POST</x:v>
       </x:c>
       <x:c r="C155" s="2" t="str">
-        <x:v>/api/notifications/read-all</x:v>
+        <x:v>/api/notifications/:id/archive</x:v>
       </x:c>
       <x:c r="D155" s="2" t="str">
-        <x:v>mark all read</x:v>
+        <x:v>archive notification</x:v>
       </x:c>
       <x:c r="E155" s="2" t="str">
         <x:v>Notifications</x:v>
       </x:c>
       <x:c r="F155" s="2" t="str">
-        <x:v>กดอ่านทั้งหมด</x:v>
+        <x:v>archive</x:v>
       </x:c>
       <x:c r="G155" s="2" t="str">
         <x:v>User</x:v>
@@ -6882,19 +6884,19 @@
         <x:v>Notifications</x:v>
       </x:c>
       <x:c r="B156" s="2" t="str">
-        <x:v>GET</x:v>
+        <x:v>PATCH</x:v>
       </x:c>
       <x:c r="C156" s="2" t="str">
-        <x:v>/api/notifications/preferences</x:v>
+        <x:v>/api/notifications/read-all</x:v>
       </x:c>
       <x:c r="D156" s="2" t="str">
-        <x:v>notification preferences</x:v>
+        <x:v>mark all read</x:v>
       </x:c>
       <x:c r="E156" s="2" t="str">
-        <x:v>Profile</x:v>
+        <x:v>Notifications</x:v>
       </x:c>
       <x:c r="F156" s="2" t="str">
-        <x:v>open settings</x:v>
+        <x:v>กดอ่านทั้งหมด</x:v>
       </x:c>
       <x:c r="G156" s="2" t="str">
         <x:v>User</x:v>
@@ -6915,19 +6917,19 @@
         <x:v>Notifications</x:v>
       </x:c>
       <x:c r="B157" s="2" t="str">
-        <x:v>PATCH</x:v>
+        <x:v>GET</x:v>
       </x:c>
       <x:c r="C157" s="2" t="str">
         <x:v>/api/notifications/preferences</x:v>
       </x:c>
       <x:c r="D157" s="2" t="str">
-        <x:v>แก้ notification preferences</x:v>
+        <x:v>notification preferences</x:v>
       </x:c>
       <x:c r="E157" s="2" t="str">
         <x:v>Profile</x:v>
       </x:c>
       <x:c r="F157" s="2" t="str">
-        <x:v>save settings</x:v>
+        <x:v>open settings</x:v>
       </x:c>
       <x:c r="G157" s="2" t="str">
         <x:v>User</x:v>
@@ -6945,25 +6947,25 @@
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
       <x:c r="A158" s="2" t="str">
-        <x:v>Media</x:v>
+        <x:v>Notifications</x:v>
       </x:c>
       <x:c r="B158" s="2" t="str">
-        <x:v>POST</x:v>
+        <x:v>PATCH</x:v>
       </x:c>
       <x:c r="C158" s="2" t="str">
-        <x:v>/api/uploads/:id/link</x:v>
+        <x:v>/api/notifications/preferences</x:v>
       </x:c>
       <x:c r="D158" s="2" t="str">
-        <x:v>ผูก media กับ owner</x:v>
+        <x:v>แก้ notification preferences</x:v>
       </x:c>
       <x:c r="E158" s="2" t="str">
-        <x:v>Any module</x:v>
+        <x:v>Profile</x:v>
       </x:c>
       <x:c r="F158" s="2" t="str">
-        <x:v>หลังสร้าง owner หรือ attach เพิ่ม</x:v>
+        <x:v>save settings</x:v>
       </x:c>
       <x:c r="G158" s="2" t="str">
-        <x:v>Owner/Admin</x:v>
+        <x:v>User</x:v>
       </x:c>
       <x:c r="H158" s="2" t="str">
         <x:v>No</x:v>
@@ -6974,28 +6976,26 @@
       <x:c r="J158" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K158" s="2" t="str">
-        <x:v>ownerType/ownerId/linkType</x:v>
-      </x:c>
+      <x:c r="K158" s="2" t="str"/>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
       <x:c r="A159" s="2" t="str">
         <x:v>Media</x:v>
       </x:c>
       <x:c r="B159" s="2" t="str">
-        <x:v>DELETE</x:v>
+        <x:v>POST</x:v>
       </x:c>
       <x:c r="C159" s="2" t="str">
         <x:v>/api/uploads/:id/link</x:v>
       </x:c>
       <x:c r="D159" s="2" t="str">
-        <x:v>ถอด media จาก owner</x:v>
+        <x:v>ผูก media กับ owner</x:v>
       </x:c>
       <x:c r="E159" s="2" t="str">
         <x:v>Any module</x:v>
       </x:c>
       <x:c r="F159" s="2" t="str">
-        <x:v>remove attachment</x:v>
+        <x:v>หลังสร้าง owner หรือ attach เพิ่ม</x:v>
       </x:c>
       <x:c r="G159" s="2" t="str">
         <x:v>Owner/Admin</x:v>
@@ -7009,76 +7009,76 @@
       <x:c r="J159" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K159" s="2" t="str"/>
+      <x:c r="K159" s="2" t="str">
+        <x:v>ownerType/ownerId/linkType</x:v>
+      </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
       <x:c r="A160" s="2" t="str">
         <x:v>Media</x:v>
       </x:c>
       <x:c r="B160" s="2" t="str">
-        <x:v>GET</x:v>
+        <x:v>DELETE</x:v>
       </x:c>
       <x:c r="C160" s="2" t="str">
-        <x:v>/api/media?ownerType=&amp;ownerId=</x:v>
+        <x:v>/api/uploads/:id/link</x:v>
       </x:c>
       <x:c r="D160" s="2" t="str">
-        <x:v>อ่าน media ของ owner</x:v>
+        <x:v>ถอด media จาก owner</x:v>
       </x:c>
       <x:c r="E160" s="2" t="str">
-        <x:v>Detail/report</x:v>
+        <x:v>Any module</x:v>
       </x:c>
       <x:c r="F160" s="2" t="str">
-        <x:v>โหลด detail</x:v>
+        <x:v>remove attachment</x:v>
       </x:c>
       <x:c r="G160" s="2" t="str">
-        <x:v>User</x:v>
+        <x:v>Owner/Admin</x:v>
       </x:c>
       <x:c r="H160" s="2" t="str">
-        <x:v>Limit</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="I160" s="2" t="str">
-        <x:v>Medium</x:v>
+        <x:v>Small</x:v>
       </x:c>
       <x:c r="J160" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K160" s="2" t="str">
-        <x:v>ตรวจสิทธิ์ตาม owner</x:v>
-      </x:c>
+      <x:c r="K160" s="2" t="str"/>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
       <x:c r="A161" s="2" t="str">
         <x:v>Media</x:v>
       </x:c>
       <x:c r="B161" s="2" t="str">
-        <x:v>POST</x:v>
+        <x:v>GET</x:v>
       </x:c>
       <x:c r="C161" s="2" t="str">
-        <x:v>/api/uploads/presign</x:v>
+        <x:v>/api/media?ownerType=&amp;ownerId=</x:v>
       </x:c>
       <x:c r="D161" s="2" t="str">
-        <x:v>ขอ signed upload URL</x:v>
+        <x:v>อ่าน media ของ owner</x:v>
       </x:c>
       <x:c r="E161" s="2" t="str">
-        <x:v>Mobile/Web</x:v>
+        <x:v>Detail/report</x:v>
       </x:c>
       <x:c r="F161" s="2" t="str">
-        <x:v>ก่อน upload direct-to-storage</x:v>
+        <x:v>โหลด detail</x:v>
       </x:c>
       <x:c r="G161" s="2" t="str">
         <x:v>User</x:v>
       </x:c>
       <x:c r="H161" s="2" t="str">
-        <x:v>No</x:v>
+        <x:v>Limit</x:v>
       </x:c>
       <x:c r="I161" s="2" t="str">
-        <x:v>Small</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="J161" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K161" s="2" t="str">
-        <x:v>optional for scale</x:v>
+        <x:v>ตรวจสิทธิ์ตาม owner</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -7089,16 +7089,16 @@
         <x:v>POST</x:v>
       </x:c>
       <x:c r="C162" s="2" t="str">
-        <x:v>/api/uploads/:id/complete</x:v>
+        <x:v>/api/uploads/presign</x:v>
       </x:c>
       <x:c r="D162" s="2" t="str">
-        <x:v>ยืนยัน upload direct-to-storage</x:v>
+        <x:v>ขอ signed upload URL</x:v>
       </x:c>
       <x:c r="E162" s="2" t="str">
         <x:v>Mobile/Web</x:v>
       </x:c>
       <x:c r="F162" s="2" t="str">
-        <x:v>หลัง upload สำเร็จ</x:v>
+        <x:v>ก่อน upload direct-to-storage</x:v>
       </x:c>
       <x:c r="G162" s="2" t="str">
         <x:v>User</x:v>
@@ -7113,27 +7113,27 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K162" s="2" t="str">
-        <x:v>verify object exists</x:v>
+        <x:v>optional for scale</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
       <x:c r="A163" s="2" t="str">
-        <x:v>Safety Culture</x:v>
+        <x:v>Media</x:v>
       </x:c>
       <x:c r="B163" s="2" t="str">
-        <x:v>GET</x:v>
+        <x:v>POST</x:v>
       </x:c>
       <x:c r="C163" s="2" t="str">
-        <x:v>/api/safety-culture/teams</x:v>
+        <x:v>/api/uploads/:id/complete</x:v>
       </x:c>
       <x:c r="D163" s="2" t="str">
-        <x:v>อ่านทีมสำหรับหน้า admin leaderboard</x:v>
+        <x:v>ยืนยัน upload direct-to-storage</x:v>
       </x:c>
       <x:c r="E163" s="2" t="str">
-        <x:v>Admin Leaderboard</x:v>
+        <x:v>Mobile/Web</x:v>
       </x:c>
       <x:c r="F163" s="2" t="str">
-        <x:v>เปิดหน้าจัดการทีม</x:v>
+        <x:v>หลัง upload สำเร็จ</x:v>
       </x:c>
       <x:c r="G163" s="2" t="str">
         <x:v>User</x:v>
@@ -7148,7 +7148,7 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K163" s="2" t="str">
-        <x:v>อ่านจาก teams และ team_members</x:v>
+        <x:v>verify object exists</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -7156,22 +7156,22 @@
         <x:v>Safety Culture</x:v>
       </x:c>
       <x:c r="B164" s="2" t="str">
-        <x:v>PUT</x:v>
+        <x:v>GET</x:v>
       </x:c>
       <x:c r="C164" s="2" t="str">
         <x:v>/api/safety-culture/teams</x:v>
       </x:c>
       <x:c r="D164" s="2" t="str">
-        <x:v>บันทึกรายการทีมสำหรับ leaderboard</x:v>
+        <x:v>อ่านทีมสำหรับหน้า admin leaderboard</x:v>
       </x:c>
       <x:c r="E164" s="2" t="str">
         <x:v>Admin Leaderboard</x:v>
       </x:c>
       <x:c r="F164" s="2" t="str">
-        <x:v>เมื่อ admin บันทึกทีม</x:v>
+        <x:v>เปิดหน้าจัดการทีม</x:v>
       </x:c>
       <x:c r="G164" s="2" t="str">
-        <x:v>Admin</x:v>
+        <x:v>User</x:v>
       </x:c>
       <x:c r="H164" s="2" t="str">
         <x:v>No</x:v>
@@ -7183,30 +7183,30 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K164" s="2" t="str">
-        <x:v>upsert/soft-delete teams</x:v>
+        <x:v>อ่านจาก teams และ team_members</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
       <x:c r="A165" s="2" t="str">
-        <x:v>Settings</x:v>
+        <x:v>Safety Culture</x:v>
       </x:c>
       <x:c r="B165" s="2" t="str">
-        <x:v>GET</x:v>
+        <x:v>PUT</x:v>
       </x:c>
       <x:c r="C165" s="2" t="str">
-        <x:v>/api/safety-settings?key=</x:v>
+        <x:v>/api/safety-culture/teams</x:v>
       </x:c>
       <x:c r="D165" s="2" t="str">
-        <x:v>อ่านค่า safety settings จากฐานจริง</x:v>
+        <x:v>บันทึกรายการทีมสำหรับ leaderboard</x:v>
       </x:c>
       <x:c r="E165" s="2" t="str">
-        <x:v>Safety Admin/DatePicker</x:v>
+        <x:v>Admin Leaderboard</x:v>
       </x:c>
       <x:c r="F165" s="2" t="str">
-        <x:v>โหลดหน้าหรือเปิด setting</x:v>
+        <x:v>เมื่อ admin บันทึกทีม</x:v>
       </x:c>
       <x:c r="G165" s="2" t="str">
-        <x:v>User</x:v>
+        <x:v>Admin</x:v>
       </x:c>
       <x:c r="H165" s="2" t="str">
         <x:v>No</x:v>
@@ -7218,7 +7218,7 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K165" s="2" t="str">
-        <x:v>ใช้ safety_settings ไม่ใช้ localStorage</x:v>
+        <x:v>upsert/soft-delete teams</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -7226,22 +7226,22 @@
         <x:v>Settings</x:v>
       </x:c>
       <x:c r="B166" s="2" t="str">
-        <x:v>PUT</x:v>
+        <x:v>GET</x:v>
       </x:c>
       <x:c r="C166" s="2" t="str">
-        <x:v>/api/safety-settings</x:v>
+        <x:v>/api/safety-settings?key=</x:v>
       </x:c>
       <x:c r="D166" s="2" t="str">
-        <x:v>บันทึกค่า safety settings ลงฐานจริง</x:v>
+        <x:v>อ่านค่า safety settings จากฐานจริง</x:v>
       </x:c>
       <x:c r="E166" s="2" t="str">
-        <x:v>Safety Admin</x:v>
+        <x:v>Safety Admin/DatePicker</x:v>
       </x:c>
       <x:c r="F166" s="2" t="str">
-        <x:v>เมื่อ admin save settings</x:v>
+        <x:v>โหลดหน้าหรือเปิด setting</x:v>
       </x:c>
       <x:c r="G166" s="2" t="str">
-        <x:v>Admin</x:v>
+        <x:v>User</x:v>
       </x:c>
       <x:c r="H166" s="2" t="str">
         <x:v>No</x:v>
@@ -7253,76 +7253,78 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K166" s="2" t="str">
-        <x:v>upsert safety_settings</x:v>
+        <x:v>ใช้ safety_settings ไม่ใช้ localStorage</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
       <x:c r="A167" s="2" t="str">
-        <x:v>Audit</x:v>
+        <x:v>Settings</x:v>
       </x:c>
       <x:c r="B167" s="2" t="str">
-        <x:v>GET</x:v>
+        <x:v>PUT</x:v>
       </x:c>
       <x:c r="C167" s="2" t="str">
-        <x:v>/api/audit-logs?actor=&amp;entity=&amp;from=&amp;to=&amp;page=&amp;pageSize=</x:v>
+        <x:v>/api/safety-settings</x:v>
       </x:c>
       <x:c r="D167" s="2" t="str">
-        <x:v>audit trail</x:v>
+        <x:v>บันทึกค่า safety settings ลงฐานจริง</x:v>
       </x:c>
       <x:c r="E167" s="2" t="str">
-        <x:v>Admin/Security</x:v>
+        <x:v>Safety Admin</x:v>
       </x:c>
       <x:c r="F167" s="2" t="str">
-        <x:v>ตรวจสอบการแก้ไข</x:v>
+        <x:v>เมื่อ admin save settings</x:v>
       </x:c>
       <x:c r="G167" s="2" t="str">
         <x:v>Admin</x:v>
       </x:c>
       <x:c r="H167" s="2" t="str">
-        <x:v>Required</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="I167" s="2" t="str">
-        <x:v>High</x:v>
+        <x:v>Small</x:v>
       </x:c>
       <x:c r="J167" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K167" s="2" t="str">
-        <x:v>ห้ามเปิด public</x:v>
+        <x:v>upsert safety_settings</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
       <x:c r="A168" s="2" t="str">
-        <x:v>System</x:v>
+        <x:v>Audit</x:v>
       </x:c>
       <x:c r="B168" s="2" t="str">
         <x:v>GET</x:v>
       </x:c>
       <x:c r="C168" s="2" t="str">
-        <x:v>/api/health</x:v>
+        <x:v>/api/audit-logs?actor=&amp;entity=&amp;from=&amp;to=&amp;page=&amp;pageSize=</x:v>
       </x:c>
       <x:c r="D168" s="2" t="str">
-        <x:v>health check</x:v>
+        <x:v>audit trail</x:v>
       </x:c>
       <x:c r="E168" s="2" t="str">
-        <x:v>Infra</x:v>
+        <x:v>Admin/Security</x:v>
       </x:c>
       <x:c r="F168" s="2" t="str">
-        <x:v>monitoring</x:v>
+        <x:v>ตรวจสอบการแก้ไข</x:v>
       </x:c>
       <x:c r="G168" s="2" t="str">
-        <x:v>Public/Internal</x:v>
+        <x:v>Admin</x:v>
       </x:c>
       <x:c r="H168" s="2" t="str">
-        <x:v>No</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="I168" s="2" t="str">
-        <x:v>Small</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="J168" s="2" t="str">
         <x:v>Existing</x:v>
       </x:c>
-      <x:c r="K168" s="2" t="str"/>
+      <x:c r="K168" s="2" t="str">
+        <x:v>ห้ามเปิด public</x:v>
+      </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
       <x:c r="A169" s="2" t="str">
@@ -7332,16 +7334,16 @@
         <x:v>GET</x:v>
       </x:c>
       <x:c r="C169" s="2" t="str">
-        <x:v>/api/version</x:v>
+        <x:v>/api/health</x:v>
       </x:c>
       <x:c r="D169" s="2" t="str">
-        <x:v>app/api version</x:v>
+        <x:v>health check</x:v>
       </x:c>
       <x:c r="E169" s="2" t="str">
-        <x:v>Infra/Debug</x:v>
+        <x:v>Infra</x:v>
       </x:c>
       <x:c r="F169" s="2" t="str">
-        <x:v>debug</x:v>
+        <x:v>monitoring</x:v>
       </x:c>
       <x:c r="G169" s="2" t="str">
         <x:v>Public/Internal</x:v>
@@ -7356,6 +7358,39 @@
         <x:v>Existing</x:v>
       </x:c>
       <x:c r="K169" s="2" t="str"/>
+    </x:row>
+    <x:row r="170" ht="15" hidden="0" customHeight="1">
+      <x:c r="A170" s="2" t="str">
+        <x:v>System</x:v>
+      </x:c>
+      <x:c r="B170" s="2" t="str">
+        <x:v>GET</x:v>
+      </x:c>
+      <x:c r="C170" s="2" t="str">
+        <x:v>/api/version</x:v>
+      </x:c>
+      <x:c r="D170" s="2" t="str">
+        <x:v>app/api version</x:v>
+      </x:c>
+      <x:c r="E170" s="2" t="str">
+        <x:v>Infra/Debug</x:v>
+      </x:c>
+      <x:c r="F170" s="2" t="str">
+        <x:v>debug</x:v>
+      </x:c>
+      <x:c r="G170" s="2" t="str">
+        <x:v>Public/Internal</x:v>
+      </x:c>
+      <x:c r="H170" s="2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I170" s="2" t="str">
+        <x:v>Small</x:v>
+      </x:c>
+      <x:c r="J170" s="2" t="str">
+        <x:v>Existing</x:v>
+      </x:c>
+      <x:c r="K170" s="2" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7364,261 +7399,305 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:cols>
+    <x:col min="1" max="1" width="13.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="6.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="26.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="27.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="41.220001220703125" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="8.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="77.66999816894531" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="44.220001220703125" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="62.33000183105469" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" t="str">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="5" t="str">
         <x:v>Use case</x:v>
       </x:c>
-      <x:c r="B1" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>Method</x:v>
       </x:c>
-      <x:c r="C1" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>Path</x:v>
       </x:c>
-      <x:c r="D1" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>Type scope</x:v>
       </x:c>
-      <x:c r="E1" t="str">
-        <x:v>Required query</x:v>
-      </x:c>
-      <x:c r="F1" t="str">
+      <x:c r="E1" s="5" t="str">
+        <x:v>Required query/body</x:v>
+      </x:c>
+      <x:c r="F1" s="5" t="str">
         <x:v>Default limit</x:v>
       </x:c>
-      <x:c r="G1" t="str">
+      <x:c r="G1" s="5" t="str">
         <x:v>Hard limit</x:v>
       </x:c>
-      <x:c r="H1" t="str">
+      <x:c r="H1" s="5" t="str">
         <x:v>Index/DB rule</x:v>
       </x:c>
-      <x:c r="I1" t="str">
+      <x:c r="I1" s="5" t="str">
         <x:v>Frontend behavior</x:v>
       </x:c>
-      <x:c r="J1" t="str">
+      <x:c r="J1" s="5" t="str">
         <x:v>Why separate</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="str">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="2" t="str">
         <x:v>โรงงาน list</x:v>
       </x:c>
-      <x:c r="B2" t="str">
+      <x:c r="B2" s="2" t="str">
         <x:v>GET</x:v>
       </x:c>
-      <x:c r="C2" t="str">
+      <x:c r="C2" s="2" t="str">
         <x:v>/api/locations/plants</x:v>
       </x:c>
-      <x:c r="D2" t="str">
+      <x:c r="D2" s="2" t="str">
         <x:v>PLANT</x:v>
       </x:c>
-      <x:c r="E2" t="str">
+      <x:c r="E2" s="2" t="str">
         <x:v>page,pageSize,search?</x:v>
       </x:c>
-      <x:c r="F2">
+      <x:c r="F2" s="2" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G2">
+      <x:c r="G2" s="2" t="n">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="H2" t="str">
+      <x:c r="H2" s="2" t="str">
         <x:v>CPAC locations mirror; source + external_key unique</x:v>
       </x:c>
-      <x:c r="I2" t="str">
+      <x:c r="I2" s="2" t="str">
         <x:v>แสดง badge RMR/Admin และปิดแก้ไขเมื่อ readOnly=true</x:v>
       </x:c>
-      <x:c r="J2" t="str">
+      <x:c r="J2" s="2" t="str">
         <x:v>ไม่ query rmr_sso.Plant ทุก request; ใช้ local ID สำหรับ Check-in</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="str">
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="2" t="str">
         <x:v>สำนักงาน list</x:v>
       </x:c>
-      <x:c r="B3" t="str">
+      <x:c r="B3" s="2" t="str">
         <x:v>GET</x:v>
       </x:c>
-      <x:c r="C3" t="str">
+      <x:c r="C3" s="2" t="str">
         <x:v>/api/locations/offices</x:v>
       </x:c>
-      <x:c r="D3" t="str">
+      <x:c r="D3" s="2" t="str">
         <x:v>OFFICE</x:v>
       </x:c>
-      <x:c r="E3" t="str">
+      <x:c r="E3" s="2" t="str">
         <x:v>page,pageSize,search?</x:v>
       </x:c>
-      <x:c r="F3">
+      <x:c r="F3" s="2" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G3">
+      <x:c r="G3" s="2" t="n">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="H3" t="str">
+      <x:c r="H3" s="2" t="str">
         <x:v>location_type + status + name/code</x:v>
       </x:c>
-      <x:c r="I3" t="str">
+      <x:c r="I3" s="2" t="str">
         <x:v>โหลดเฉพาะ tab สำนักงาน</x:v>
       </x:c>
-      <x:c r="J3" t="str">
+      <x:c r="J3" s="2" t="str">
         <x:v>ข้อมูลคนละ pattern กับโรงงาน</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="str">
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="2" t="str">
         <x:v>site งาน list</x:v>
       </x:c>
-      <x:c r="B4" t="str">
+      <x:c r="B4" s="2" t="str">
         <x:v>GET</x:v>
       </x:c>
-      <x:c r="C4" t="str">
+      <x:c r="C4" s="2" t="str">
         <x:v>/api/locations/sites</x:v>
       </x:c>
-      <x:c r="D4" t="str">
+      <x:c r="D4" s="2" t="str">
         <x:v>SITE</x:v>
       </x:c>
-      <x:c r="E4" t="str">
+      <x:c r="E4" s="2" t="str">
         <x:v>page,pageSize,search?</x:v>
       </x:c>
-      <x:c r="F4">
+      <x:c r="F4" s="2" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G4">
+      <x:c r="G4" s="2" t="n">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="H4" t="str">
+      <x:c r="H4" s="2" t="str">
         <x:v>location_type + status + name/code</x:v>
       </x:c>
-      <x:c r="I4" t="str">
+      <x:c r="I4" s="2" t="str">
         <x:v>โหลดเฉพาะ tab site</x:v>
       </x:c>
-      <x:c r="J4" t="str">
+      <x:c r="J4" s="2" t="str">
         <x:v>site อาจหลักแสนและเปลี่ยนบ่อย</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="str">
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="2" t="str">
         <x:v>map markers</x:v>
       </x:c>
-      <x:c r="B5" t="str">
+      <x:c r="B5" s="2" t="str">
         <x:v>GET</x:v>
       </x:c>
-      <x:c r="C5" t="str">
+      <x:c r="C5" s="2" t="str">
         <x:v>/api/locations/map</x:v>
       </x:c>
-      <x:c r="D5" t="str">
+      <x:c r="D5" s="2" t="str">
         <x:v>PLANT/OFFICE/SITE/CUSTOM/all</x:v>
       </x:c>
-      <x:c r="E5" t="str">
+      <x:c r="E5" s="2" t="str">
         <x:v>bbox,zoom,type?</x:v>
       </x:c>
-      <x:c r="F5">
+      <x:c r="F5" s="2" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="G5">
+      <x:c r="G5" s="2" t="n">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="H5" t="str">
+      <x:c r="H5" s="2" t="str">
         <x:v>spatial index on position</x:v>
       </x:c>
-      <x:c r="I5" t="str">
+      <x:c r="I5" s="2" t="str">
         <x:v>เรียกทุกครั้งเมื่อ pan/zoom หลัง debounce</x:v>
       </x:c>
-      <x:c r="J5" t="str">
+      <x:c r="J5" s="2" t="str">
         <x:v>แผนที่ต้องคืนเฉพาะ viewport</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str">
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="2" t="str">
         <x:v>autocomplete</x:v>
       </x:c>
-      <x:c r="B6" t="str">
+      <x:c r="B6" s="2" t="str">
         <x:v>GET</x:v>
       </x:c>
-      <x:c r="C6" t="str">
+      <x:c r="C6" s="2" t="str">
         <x:v>/api/locations/search</x:v>
       </x:c>
-      <x:c r="D6" t="str">
+      <x:c r="D6" s="2" t="str">
         <x:v>type optional</x:v>
       </x:c>
-      <x:c r="E6" t="str">
+      <x:c r="E6" s="2" t="str">
         <x:v>q,type?,limit</x:v>
       </x:c>
-      <x:c r="F6">
+      <x:c r="F6" s="2" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G6">
+      <x:c r="G6" s="2" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="H6" t="str">
+      <x:c r="H6" s="2" t="str">
         <x:v>prefix/fulltext index</x:v>
       </x:c>
-      <x:c r="I6" t="str">
+      <x:c r="I6" s="2" t="str">
         <x:v>เรียกหลังพิมพ์ 2-3 ตัวอักษร</x:v>
       </x:c>
-      <x:c r="J6" t="str">
+      <x:c r="J6" s="2" t="str">
         <x:v>ไม่โหลด dropdown ทั้งหมด</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="2" t="str">
         <x:v>detail</x:v>
       </x:c>
-      <x:c r="B7" t="str">
+      <x:c r="B7" s="2" t="str">
         <x:v>GET</x:v>
       </x:c>
-      <x:c r="C7" t="str">
+      <x:c r="C7" s="2" t="str">
         <x:v>/api/locations/:id</x:v>
       </x:c>
-      <x:c r="D7" t="str">
+      <x:c r="D7" s="2" t="str">
         <x:v>single</x:v>
       </x:c>
-      <x:c r="E7" t="str">
+      <x:c r="E7" s="2" t="str">
         <x:v>none</x:v>
       </x:c>
-      <x:c r="F7">
+      <x:c r="F7" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G7">
+      <x:c r="G7" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H7" t="str">
+      <x:c r="H7" s="2" t="str">
         <x:v>PK</x:v>
       </x:c>
-      <x:c r="I7" t="str">
+      <x:c r="I7" s="2" t="str">
         <x:v>โหลดเมื่อเลือก marker/card</x:v>
       </x:c>
-      <x:c r="J7" t="str">
+      <x:c r="J7" s="2" t="str">
         <x:v>ลด payload list</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="str">
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="2" t="str">
         <x:v>check-in submit</x:v>
       </x:c>
-      <x:c r="B8" t="str">
+      <x:c r="B8" s="2" t="str">
         <x:v>POST</x:v>
       </x:c>
-      <x:c r="C8" t="str">
+      <x:c r="C8" s="2" t="str">
         <x:v>/api/checkins</x:v>
       </x:c>
-      <x:c r="D8" t="str">
-        <x:v>selected location</x:v>
-      </x:c>
-      <x:c r="E8" t="str">
-        <x:v>body</x:v>
-      </x:c>
-      <x:c r="F8">
+      <x:c r="D8" s="2" t="str">
+        <x:v>selected location + actual GPS</x:v>
+      </x:c>
+      <x:c r="E8" s="2" t="str">
+        <x:v>locationId, actualLat, actualLng, actualAccuracyM?</x:v>
+      </x:c>
+      <x:c r="F8" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G8">
+      <x:c r="G8" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H8" t="str">
-        <x:v>user/date/location</x:v>
-      </x:c>
-      <x:c r="I8" t="str">
+      <x:c r="H8" s="2" t="str">
+        <x:v>writes actual_position + actual_location_*_snapshot + distance/match status</x:v>
+      </x:c>
+      <x:c r="I8" s="2" t="str">
         <x:v>ส่งหลังยืนยันตำแหน่ง</x:v>
       </x:c>
-      <x:c r="J8" t="str">
-        <x:v>แยก write ออกจาก location master</x:v>
+      <x:c r="J8" s="2" t="str">
+        <x:v>แยก write ออกจาก location master และเก็บ snapshot เพื่อประวัติย้อนหลังไม่เปลี่ยน</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="2" t="str">
+        <x:v>check-in history</x:v>
+      </x:c>
+      <x:c r="B9" s="2" t="str">
+        <x:v>GET</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="str">
+        <x:v>/api/checkins | /api/checkins/me</x:v>
+      </x:c>
+      <x:c r="D9" s="2" t="str">
+        <x:v>user/location/date</x:v>
+      </x:c>
+      <x:c r="E9" s="2" t="str">
+        <x:v>userId?,locationId?,from?,to?,page,pageSize</x:v>
+      </x:c>
+      <x:c r="F9" s="2" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G9" s="2" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H9" s="2" t="str">
+        <x:v>idx_checkins_user_time_id, idx_checkins_location_time_id, idx_checkins_actual_location_time_id</x:v>
+      </x:c>
+      <x:c r="I9" s="2" t="str">
+        <x:v>ใช้ตรวจสอบประวัติ/รายงาน</x:v>
+      </x:c>
+      <x:c r="J9" s="2" t="str">
+        <x:v>อ่าน selected + actual GPS + actual location snapshot</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8316,7 +8395,7 @@
     <x:col min="2" max="2" width="52.220001220703125" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="90.77999877929688" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="9.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="68.66999816894531" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="100.77999877929688" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -8401,7 +8480,7 @@
         <x:v>Write/Read</x:v>
       </x:c>
       <x:c r="E5" s="2" t="str">
-        <x:v>selected vs actual GPS</x:v>
+        <x:v>selected location, actual GPS, nearest actual location snapshot</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -8412,13 +8491,13 @@
         <x:v>safety_effort_submissions</x:v>
       </x:c>
       <x:c r="C6" s="2" t="str">
-        <x:v>safety_old, users</x:v>
+        <x:v>safety_old, users, checkins</x:v>
       </x:c>
       <x:c r="D6" s="2" t="str">
         <x:v>Write/Read</x:v>
       </x:c>
       <x:c r="E6" s="2" t="str">
-        <x:v>dashboard/category รวมข้อมูลใหม่และ legacy</x:v>
+        <x:v>dashboard/category รวมข้อมูลใหม่และ legacy; report history อ่าน actual_location_*_snapshot จาก checkins ก่อน fallback nearest</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
